--- a/content/Question Bank/Coding Questions/Unit 3 - Control Flow/Unit 3 - Control Flow - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 3 - Control Flow/Unit 3 - Control Flow - Coding Questions.xlsx
@@ -596,13 +596,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>An exam hall coordinator checks a student's marks to decide if they pass. Write a program that reads a student's marks and prints whether they passed, using a passing mark of 40.
+          <t>Results are out, and the exam hall coordinator has a long list of marks to sort into pass and fail before the revaluation window opens. The university's rule is simple: 40 marks or more is a pass.
+Write a program that reads a student's marks and prints exactly `Pass` if the marks are 40 or more, and exactly `Fail` otherwise.
 ### Input Format
 - Line 1: Marks
 ### Output Format
 ```
 Pass
 ```
+### Example Walkthrough
+In the sample, the marks are 55. Since 55 is greater than or equal to 40, the passing condition is true, so the program prints `Pass`. Marks of 39 would instead print `Fail`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -743,13 +746,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The gym assigns lockers and wants to label each one as even or odd for the two locker rows. Write a program that reads a locker number and prints whether it is even or odd.
+          <t>The campus gym has two rows of lockers: even-numbered lockers along the left wall and odd-numbered ones along the right. When a student is assigned a locker, the app must tell them which row to walk to.
+Write a program that reads a locker number and prints `Even` if the number is even and `Odd` if it is odd. A number is even when dividing it by 2 leaves no remainder - that is, nothing is left over.
 ### Input Format
 - Line 1: Locker number
 ### Output Format
 ```
 Even
 ```
+### Example Walkthrough
+In the sample, the locker number is 24. Dividing 24 by 2 leaves a remainder of 0, so the number is even and the program prints `Even`. A locker like 7 leaves a remainder of 1, so it would print `Odd`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -890,13 +896,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>An election helpdesk checks whether a citizen is old enough to vote. Write a program that reads a citizen's age and prints whether they are eligible to vote, using 18 as the minimum voting age.
+          <t>It is election season, and volunteers at the local helpdesk answer one question all day: "Am I old enough to vote?" In India the answer depends on a single number - you must be at least 18.
+Write a program that reads a citizen's age and prints exactly `Eligible to vote` if the age is 18 or more, and exactly `Not eligible to vote` otherwise.
 ### Input Format
 - Line 1: Age
 ### Output Format
 ```
 Eligible to vote
 ```
+### Example Walkthrough
+In the sample, the age is 19. Since 19 is at least 18, the condition is satisfied and the program prints `Eligible to vote`. An age of 17 would print `Not eligible to vote` instead.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1037,13 +1046,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>An online store offers a discount once a shopper's cart total crosses a minimum amount. Write a program that reads a cart total and prints whether it is eligible for a discount, using 1000 as the minimum amount.
+          <t>During its monsoon sale, an online store gives a discount to anyone whose cart total reaches Rs.1000. As shoppers keep adding items, the cart page keeps checking whether they have crossed the line.
+Write a program that reads the cart total and prints exactly `Eligible for discount` if the total is 1000 or more, and exactly `No discount` otherwise.
 ### Input Format
 - Line 1: Cart total
 ### Output Format
 ```
 Eligible for discount
 ```
+### Example Walkthrough
+In the sample, the cart total is 1500. Since 1500 is at least 1000, the shopper qualifies and the program prints `Eligible for discount`. A total of 750 would print `No discount`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1184,7 +1196,8 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A report card generator assigns a letter grade based on marks, but attendance shortfalls override everything. Write a program that reads a student's marks and attendance percentage, then prints their grade. If attendance is below 75 percent, the grade is capped at 'D' no matter how high the marks are. Otherwise the grade is decided by marks: 'A' for 90 or above, 'B' for 75 up to 90, 'C' for 60 up to 75, and 'D' below 60.
+          <t>The report card generator at a college assigns letter grades from marks, but there is a catch: a student with poor attendance cannot get a good grade no matter how well they scored. The attendance check is applied first, before marks are even looked at.
+Write a program that reads a student's marks and attendance percentage. If the attendance is below 75, print `D` regardless of the marks. Otherwise grade by marks: `A` for 90 or above, `B` for 75 up to (but not including) 90, `C` for 60 up to (but not including) 75, and `D` below 60.
 ### Input Format
 - Line 1: Marks
 - Line 2: Attendance percentage
@@ -1192,6 +1205,8 @@
 ```
 D
 ```
+### Example Walkthrough
+In the sample, the marks are 95 and the attendance is 60. Because 60 is below 75, the attendance rule kicks in first and caps the grade, so the program prints `D` - even though 95 marks would normally earn an `A`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1347,7 +1362,8 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>An ATM approves a withdrawal only if there are sufficient funds and the amount is a multiple of 100. Write a program that reads the account balance and the requested withdrawal amount, then prints whether the withdrawal is approved.
+          <t>Sneha is at an ATM trying to withdraw cash. The machine approves a withdrawal only when two things are both true: her balance covers the amount, and the amount is a multiple of 100, because the machine only holds Rs.100 notes.
+Write a program that reads the account balance and the withdrawal amount, then prints exactly `Approved` if the amount is no more than the balance and is a multiple of 100 (dividing it by 100 leaves no remainder); otherwise print exactly `Denied`.
 ### Input Format
 - Line 1: Account balance
 - Line 2: Withdrawal amount
@@ -1355,6 +1371,8 @@
 ```
 Approved
 ```
+### Example Walkthrough
+In the sample, the balance is 5000 and the request is 2000. First check: 2000 is not more than 5000, so the funds are sufficient. Second check: 2000 divided by 100 leaves no remainder, so it is a valid multiple. Both checks pass, and the program prints `Approved`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1503,14 +1521,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A cab app applies a surge multiplier that depends on both the day type and the time of day. Write a program that reads the day type ('weekday' or 'weekend') and the hour of the day (0-23), then prints the surge multiplier. Peak hours are 8 to 10 and 17 to 19 (inclusive on both ends). On weekends the surge is 2.0 during peak hours and 1.2 otherwise. On weekdays the surge is 1.5 during peak hours and 1.0 otherwise. Print the multiplier with exactly one digit after the decimal point.
+          <t>A cab app raises its fare multiplier during busy hours, and weekends behave differently from weekdays. Before showing the fare, the pricing engine looks at two things - what kind of day it is and what hour it is - and then picks the multiplier.
+Write a program that reads the day type (`weekday` or `weekend`) and the hour of the day (0-23), then prints the surge multiplier. Peak hours are 8 to 10 and 17 to 19 (inclusive on both ends). On weekends the surge is 2.0 during peak hours and 1.2 otherwise; on weekdays it is 1.5 during peak hours and 1.0 otherwise. Print the multiplier with exactly one digit after the decimal point.
 ### Input Format
-- Line 1: Day type ('weekday' or 'weekend')
+- Line 1: Day type (`weekday` or `weekend`)
 - Line 2: Hour (0-23)
 ### Output Format
 ```
 1.5
 ```
+### Example Walkthrough
+In the sample, the day type is `weekday` and the hour is 9. Since 9 falls inside the morning peak window of 8 to 10, this is a weekday peak-hour ride, so the multiplier is 1.5 and the program prints `1.5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1661,13 +1682,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A quick-feedback tool shows only a Pass/Fail label using a single conditional expression instead of a full if-else block. Write a program that reads a student's marks and prints 'Pass' if the marks are at least 40, and 'Fail' otherwise, using a ternary (conditional) expression.
+          <t>A quick-feedback kiosk outside the exam hall shows students a single word - Pass or Fail - the moment they enter their marks. The developer wants the check written in one line using Python's conditional (ternary) expression instead of a full `if-else` block.
+Write a program that reads a student's marks and prints exactly `Pass` if the marks are 40 or more, and exactly `Fail` otherwise, using a one-line conditional expression of the form: `result = "Pass" if marks &gt;= 40 else "Fail"`.
 ### Input Format
 - Line 1: Marks
 ### Output Format
 ```
 Pass
 ```
+### Example Walkthrough
+In the sample, the marks are 72. The condition `72 &gt;= 40` is true, so the conditional expression picks `Pass` and the program prints it. Marks of 25 would make the condition false and print `Fail`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1806,15 +1830,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A scoreboard needs to highlight the highest of three submitted scores using nested decision checks. Write a program that reads three numbers and prints the largest one, using nested if statements rather than a built-in maximum function.
+          <t>Three teams have just submitted their scores at the college quiz finals, and the scoreboard must highlight the highest one. As practice with decision-making, the organisers want the comparison done with nested `if` statements - an `if` inside another `if` - rather than Python's built-in `max` function.
+Write a program that reads three numbers (read them as decimal numbers) and prints the largest one in the form `Largest: &lt;largest&gt;`.
 ### Input Format
 - Line 1: First number
 - Line 2: Second number
 - Line 3: Third number
 ### Output Format
 ```
-Largest: &lt;largest&gt;
-```
+Largest: 27.0
+```
+### Example Walkthrough
+In the sample, the three numbers are 12, 27, and 19. Comparing the first two, 27 beats 12; comparing that winner with 19, 27 is still bigger. Since the numbers are read as decimals, the program prints `Largest: 27.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1978,7 +2005,8 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A loan officer approves an application if the applicant either has a high income or has both a decent income and a co-signer. Write a program that reads an applicant's monthly income and whether they have a co-signer (1 for yes, 0 for no), then prints the loan decision. The loan is approved if the income is at least 50000, or if the income is at least 25000 and there is a co-signer.
+          <t>A loan officer at a bank follows a two-path rule for personal loans: a high earner is approved on income alone, while a moderate earner still qualifies if someone co-signs the loan with them. Every other application is rejected.
+Write a program that reads the applicant's monthly income and whether they have a co-signer (1 for yes, 0 for no). Print exactly `Approved` if the income is at least 50000, or if the income is at least 25000 and there is a co-signer; otherwise print exactly `Rejected`.
 ### Input Format
 - Line 1: Monthly income
 - Line 2: Has co-signer (1 or 0)
@@ -1986,6 +2014,8 @@
 ```
 Approved
 ```
+### Example Walkthrough
+In the sample, the income is 60000 with no co-signer (0). The first path already succeeds because 60000 is at least 50000, so the missing co-signer does not matter and the program prints `Approved`. An income of 40000 with no co-signer would satisfy neither path and print `Rejected`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>

--- a/content/Question Bank/Coding Questions/Unit 3 - Control Flow/Unit 3 - Control Flow - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 3 - Control Flow/Unit 3 - Control Flow - Coding Questions.xlsx
@@ -1,13 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH31"/>
+  <dimension ref="A1:AH11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -621,12 +624,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -636,7 +649,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>if-else</t>
+          <t>conditional-statements</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -771,12 +784,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -786,7 +809,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>if-else</t>
+          <t>conditional-statements</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -921,12 +944,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -936,7 +969,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>if-else</t>
+          <t>conditional-statements</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1071,12 +1104,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1086,7 +1129,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>if-else</t>
+          <t>conditional-statements</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1222,12 +1265,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1237,7 +1290,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>if-else</t>
+          <t>nested-conditions</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1388,12 +1441,22 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1403,7 +1466,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>if-else</t>
+          <t>conditional-statements</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1547,12 +1610,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1562,7 +1635,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>if-else</t>
+          <t>nested-conditions</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1707,12 +1780,22 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1722,7 +1805,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>if-else</t>
+          <t>conditional-expressions</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1825,10 +1908,504 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Python - Even Entry Check</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Even Entry Check. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Token
+### Output Format
+```
+Eligible
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>control-flow</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>conditional-statements</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Eligible</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Eligible</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Eligible</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Eligible</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>n=int(input())
+print("Eligible" if n%2==0 else "Not Eligible")</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Pass Fail Label</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Pass Fail Label. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Score
+### Output Format
+```
+Pass
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>control-flow</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>conditional-statements</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>s=int(input())
+print("Pass" if s&gt;=40 else "Fail")</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>Python - Largest of Three Numbers</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Three teams have just submitted their scores at the college quiz finals, and the scoreboard must highlight the highest one. As practice with decision-making, the organisers want the comparison done with nested `if` statements - an `if` inside another `if` - rather than Python's built-in `max` function.
 Write a program that reads three numbers (read them as decimal numbers) and prints the largest one in the form `Largest: &lt;largest&gt;`.
@@ -1847,138 +2424,148 @@
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>if-else</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>nested-conditions</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>12
 27
 19</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Largest: 27.0</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>5
 5
 5</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Largest: 5.0</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>100
 20
 300</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Largest: 300.0</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>1
 2
 3</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Largest: 3.0</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>3
 2
 1</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Largest: 3.0</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>2
 3
 1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>Largest: 3.0</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>-5
 -2
 -8</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Largest: -2.0</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>a = float(input())
 b = float(input())
@@ -1997,13 +2584,13 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Multi-Condition Loan Approval</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>A loan officer at a bank follows a two-path rule for personal loans: a high earner is approved on income alone, while a moderate earner still qualifies if someone co-signs the loan with them. Every other application is rejected.
 Write a program that reads the applicant's monthly income and whether they have a co-signer (1 for yes, 0 for no). Print exactly `Approved` if the income is at least 50000, or if the income is at least 25000 and there is a co-signer; otherwise print exactly `Rejected`.
@@ -2021,131 +2608,141 @@
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>if-else</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>truthiness-and-boolean-logic</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>60000
 0</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>30000
 1</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>20000
 1</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>50000
 1</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>25000
 1</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>24999
 1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>40000
 0</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>income = float(input())
 has_cosigner = int(input())
@@ -2156,13 +2753,13 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Login Access Check</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>A members-only portal checks a flag to decide whether to grant access. Write a program that reads whether the user is a member (1 for yes, 0 for no) and prints whether access is granted.
 ### Input Format
@@ -2171,129 +2768,141 @@
 ```
 Access Granted
 ```
+### Example Walkthrough
+In the sample, the member flag is `1`. Since `is_member == 1` is `True`, the program prints `Access Granted`. A flag of `0` would print `Access Denied` instead.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>if-else</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>conditional-statements</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O12" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P12" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="b">
-        <v>1</v>
-      </c>
-      <c r="R12" t="inlineStr">
+      <c r="P4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Access Granted</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Access Denied</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Access Granted</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Access Granted</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Access Denied</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>Access Granted</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>Access Denied</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>is_member = int(input())
 if is_member == 1:
@@ -2303,13 +2912,13 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Age-Based Movie Ticket</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>A cinema counter issues either a child or an adult ticket based on the customer's age. Write a program that reads a customer's age and prints which ticket type they should be issued, using 18 as the cutoff age for an adult ticket.
 ### Input Format
@@ -2318,129 +2927,141 @@
 ```
 Adult Ticket
 ```
+### Example Walkthrough
+In the sample, the age is `25`. Since `25 &gt;= 18`, the program prints `Adult Ticket`. An age below `18` would print `Child Ticket` instead.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>if-else</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>conditional-statements</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O13" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P13" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="b">
-        <v>1</v>
-      </c>
-      <c r="R13" t="inlineStr">
+      <c r="P5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>Adult Ticket</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Child Ticket</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Adult Ticket</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Child Ticket</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Adult Ticket</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>Child Ticket</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="AE13" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>Adult Ticket</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>age = int(input())
 if age &gt;= 18:
@@ -2450,13 +3071,13 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Weather Umbrella Advice</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>A weather app gives a simple reminder based on whether it is currently raining. Write a program that reads whether it is raining (1 for yes, 0 for no) and prints the appropriate advice.
 ### Input Format
@@ -2465,129 +3086,141 @@
 ```
 Carry an umbrella
 ```
+### Example Walkthrough
+In the sample, the rain flag is `1`. Since `is_raining == 1` is `True`, the program prints `Carry an umbrella`. A flag of `0` would print `No umbrella needed` instead.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>if-else</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>conditional-statements</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O14" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P14" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="b">
-        <v>1</v>
-      </c>
-      <c r="R14" t="inlineStr">
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>Carry an umbrella</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>No umbrella needed</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Carry an umbrella</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>No umbrella needed</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Carry an umbrella</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>No umbrella needed</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>Carry an umbrella</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>is_raining = int(input())
 if is_raining == 1:
@@ -2597,13 +3230,13 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Account Balance Status</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>A banking app labels an account as overdrawn if its balance has gone below zero. Write a program that reads an account balance and prints whether the account is overdrawn or in credit.
 ### Input Format
@@ -2612,129 +3245,141 @@
 ```
 In Credit
 ```
+### Example Walkthrough
+In the sample, the balance is `1500`. Since `1500` is not less than `0`, the account is not overdrawn, so the program prints `In Credit`. A negative balance would print `Overdrawn` instead.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>if-else</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>conditional-statements</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O15" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P15" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="b">
-        <v>1</v>
-      </c>
-      <c r="R15" t="inlineStr">
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>In Credit</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>-200</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Overdrawn</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>In Credit</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>-0.01</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Overdrawn</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>In Credit</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>-9999</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>Overdrawn</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE15" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>In Credit</t>
         </is>
       </c>
-      <c r="AG15" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>balance = float(input())
 if balance &lt; 0:
@@ -2744,13 +3389,13 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Library Book Return Status</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>The library front desk checks how many days late a returned book is to flag overdue returns. Write a program that reads the number of days a book is late and prints whether it is overdue or on time.
 ### Input Format
@@ -2759,129 +3404,141 @@
 ```
 Overdue
 ```
+### Example Walkthrough
+In the sample, the book is `5` days late. Since `5 &gt; 0`, the program prints `Overdue`. A value of `0` or less would print `On Time` instead.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>if-else</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>conditional-statements</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O16" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P16" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="b">
-        <v>1</v>
-      </c>
-      <c r="R16" t="inlineStr">
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>Overdue</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>On Time</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Overdue</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>On Time</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Overdue</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>Overdue</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>Overdue</t>
         </is>
       </c>
-      <c r="AG16" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>days_late = int(input())
 if days_late &gt; 0:
@@ -2891,13 +3548,13 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Python - Temperature Comfort Check</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>A smart thermostat decides whether a room feels hot based on the current temperature. Write a program that reads a temperature in Celsius and prints whether it is hot or comfortable, using 30 as the threshold for hot.
 ### Input Format
@@ -2906,129 +3563,141 @@
 ```
 Hot
 ```
+### Example Walkthrough
+In the sample, the temperature is `35`. Since `35 &gt; 30`, the program prints `Hot`. A temperature of `30` or below would print `Comfortable` instead.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D9" t="n">
         <v>5</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>if-else</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>conditional-statements</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O17" t="b">
+      <c r="O9" t="b">
         <v>0</v>
       </c>
-      <c r="P17" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q17" t="b">
-        <v>1</v>
-      </c>
-      <c r="R17" t="inlineStr">
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Comfortable</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Comfortable</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>30.01</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>29.99</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Comfortable</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>Comfortable</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="AE17" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>temp = float(input())
 if temp &gt; 30:
@@ -3038,13 +3707,516 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Temperature Alert</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Temperature Alert. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Temperature
+### Output Format
+```
+Hot
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>control-flow</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>conditional-statements</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>t=float(input())
+print("Hot" if t&gt;35 else "Normal")</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Largest of Two</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Largest of Two. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: First
+- Line 2: Second
+### Output Format
+```
+5
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>control-flow</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>conditional-statements</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>5
+3</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2
+9</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>7
+7</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>-1
+-5</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>0
+10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>100
+99</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>-3
+4</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>a=int(input())
+b=int(input())
+print(a if a&gt;=b else b)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Python - Parking Fee Tier</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>A mall's parking lot charges by vehicle type with a free grace period. Write a program that reads the number of hours a vehicle was parked and the vehicle type ('car' or 'bike'), then prints the total parking fee. Bikes get the first 2 hours free and are charged Rs. 5 per hour after that. Cars get only the first 1 hour free and are charged Rs. 10 per hour after that.
 ### Input Format
@@ -3054,136 +4226,148 @@
 ```
 0
 ```
+### Example Walkthrough
+In the sample, a bike is parked for `1` hour, well within its `2`-hour free window, so the fee is `0` and the program prints `0`. Parking for `5` hours would instead charge `(5 - 2) x 5 = 15`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>if-else</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>nested-conditions</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O18" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P18" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q18" t="b">
-        <v>1</v>
-      </c>
-      <c r="R18" t="inlineStr">
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>1
 car</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>5
 car</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>2
 bike</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>6
 bike</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>0
 car</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>1
 bike</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>10
 car</t>
         </is>
       </c>
-      <c r="AE18" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="AG18" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>hours = int(input())
 vehicle_type = input()
@@ -3201,13 +4385,13 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - BMI Category</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>A fitness app classifies a member's BMI into a category, but seniors get slightly lower thresholds. Write a program that reads a BMI value and the member's age, then prints the BMI category. For members aged 60 or above, the boundaries are lowered by 1: 'Underweight' below 17, 'Normal' from 17 up to 24, 'Overweight' from 24 up to 28, and 'Obese' from 28 upward. For members under 60, the usual boundaries apply: 'Underweight' below 18.5, 'Normal' from 18.5 up to 25, 'Overweight' from 25 up to 30, and 'Obese' from 30 upward.
 ### Input Format
@@ -3217,136 +4401,148 @@
 ```
 Normal
 ```
+### Example Walkthrough
+In the sample, the BMI is `22` and the age is `30`, so the under-60 boundaries apply. Since `22` falls between `18.5` and `25`, the category is `Normal`, and the program prints `Normal`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>if-else</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>nested-conditions</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O19" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P19" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q19" t="b">
-        <v>1</v>
-      </c>
-      <c r="R19" t="inlineStr">
+      <c r="P3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>22
 30</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>18
 65</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>17.5
 70</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>16.5
 65</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Underweight</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>26
 62</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Overweight</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>29
 61</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>Obese</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>32
 40</t>
         </is>
       </c>
-      <c r="AE19" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>Obese</t>
         </is>
       </c>
-      <c r="AG19" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>bmi = float(input())
 age = int(input())
@@ -3372,13 +4568,13 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Ticket Pricing by Age Group</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>An amusement park prices tickets by age group and adds a weekend surcharge. Write a program that reads a visitor's age and whether the visit is on a weekend ('yes' or 'no'), then prints the final ticket price. The base price by age is: free (0) under 5, 100 from 5 up to 18, 200 from 18 up to 60, and 150 from 60 upward. If the visit is on a weekend, a flat surcharge of 50 is added to any non-zero base price; a free ticket stays free.
 ### Input Format
@@ -3388,136 +4584,148 @@
 ```
 0
 ```
+### Example Walkthrough
+In the sample, the age is `3` and it is not a weekend. Since the age is under `5`, the base price is `0`, and a free ticket stays free even with a surcharge, so the program prints `0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>if-else</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>nested-conditions</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O20" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P20" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q20" t="b">
-        <v>1</v>
-      </c>
-      <c r="R20" t="inlineStr">
+      <c r="P4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>3
 yes</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>10
 no</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>10
 yes</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>30
 no</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>30
 yes</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>65
 yes</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>4
 no</t>
         </is>
       </c>
-      <c r="AE20" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AG20" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>age = int(input())
 is_weekend = input()
@@ -3535,13 +4743,13 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Exam Result with Attendance</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>A college only passes a student if their marks clear 40 and their attendance is at least 75 percent. Write a program that reads a student's marks and attendance percentage, then prints whether the student passed.
 ### Input Format
@@ -3551,136 +4759,148 @@
 ```
 Pass
 ```
+### Example Walkthrough
+In the sample, the marks are `65` and the attendance is `80`. Since `65 &gt;= 40` and `80 &gt;= 75` are both `True`, the program prints `Pass`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>if-else</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>truthiness-and-boolean-logic</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O21" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P21" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q21" t="b">
-        <v>1</v>
-      </c>
-      <c r="R21" t="inlineStr">
+      <c r="P5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>60
 80</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>60
 50</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>30
 90</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>39.9
 90</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>40
 74.9</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>40
 75</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="AD21" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>100
 100</t>
         </is>
       </c>
-      <c r="AE21" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="AG21" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>marks = float(input())
 attendance = float(input())
@@ -3691,13 +4911,13 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Seat Belt Reminder</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>A car's dashboard shows a seat belt warning only while the car is moving and the belt is unfastened. Write a program that reads the car's speed and whether the seat belt is fastened (1 for yes, 0 for no), then prints whether the warning should be shown.
 ### Input Format
@@ -3707,136 +4927,148 @@
 ```
 Show Warning
 ```
+### Example Walkthrough
+In the sample, the speed is `40` and the belt flag is `0`. Since the car is moving and the belt is unfastened, the program prints `Show Warning`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>if-else</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>truthiness-and-boolean-logic</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O22" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P22" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q22" t="b">
-        <v>1</v>
-      </c>
-      <c r="R22" t="inlineStr">
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>40
 0</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>Show Warning</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>No Warning</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>40
 1</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>No Warning</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>0.1
 0</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Show Warning</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>10
 1</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>No Warning</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>0
 1</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>No Warning</t>
         </is>
       </c>
-      <c r="AD22" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>100
 0</t>
         </is>
       </c>
-      <c r="AE22" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>Show Warning</t>
         </is>
       </c>
-      <c r="AG22" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>speed = float(input())
 belt_fastened = int(input())
@@ -3847,13 +5079,13 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Login Attempts Lockout</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>A banking app locks accounts after too many failed login attempts, but admin accounts are given a much higher threshold. Write a program that reads the number of failed login attempts and whether the account is an admin account ('yes' or 'no'), then prints the account status. Regular accounts are locked once attempts exceed 3; admin accounts are locked only once attempts exceed 10. Print 'Locked' if the account is locked, otherwise print 'Allowed'.
 ### Input Format
@@ -3863,136 +5095,148 @@
 ```
 Allowed
 ```
+### Example Walkthrough
+In the sample, there are `2` failed attempts on a non-admin account. Since `2` does not exceed the regular threshold of `3`, the program prints `Allowed`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>if-else</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>nested-conditions</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O23" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P23" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q23" t="b">
-        <v>1</v>
-      </c>
-      <c r="R23" t="inlineStr">
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>2
 no</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>Allowed</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>4
 no</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>3
 no</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Allowed</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>10
 yes</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Allowed</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>11
 yes</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>5
 yes</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>Allowed</t>
         </is>
       </c>
-      <c r="AD23" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>0
 no</t>
         </is>
       </c>
-      <c r="AE23" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>Allowed</t>
         </is>
       </c>
-      <c r="AG23" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>attempts = int(input())
 is_admin = input()
@@ -4004,13 +5248,13 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Shipping Cost Bracket</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>A delivery company charges shipping cost by weight bracket, with a discount for premium members. Write a program that reads a package's weight in kilograms and the customer's membership status ('Premium' or 'Regular'), then prints the shipping cost. The regular bracket price is 50 for up to 1 kg, 100 for up to 5 kg, and 200 for anything heavier. Premium members get a flat 30 percent discount off the regular bracket price, rounded down to the nearest whole number.
 ### Input Format
@@ -4020,136 +5264,148 @@
 ```
 50
 ```
+### Example Walkthrough
+In the sample, the weight is `0.5` kg for a Regular member. Since `0.5` is at most `1` kg, the regular bracket price of `50` applies with no discount, so the program prints `50`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>if-else</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>nested-conditions</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O24" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P24" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q24" t="b">
-        <v>1</v>
-      </c>
-      <c r="R24" t="inlineStr">
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>0.5
 Regular</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>0.5
 Premium</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>3
 Regular</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>3
 Premium</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>7
 Regular</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>7
 Premium</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>140</t>
         </is>
       </c>
-      <c r="AD24" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>1
 Premium</t>
         </is>
       </c>
-      <c r="AE24" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="AG24" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>weight = float(input())
 membership_status = input()
@@ -4165,13 +5421,679 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Python - Grade Band</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Grade Band. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Score
+### Output Format
+```
+A
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>control-flow</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>nested-conditions</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Needs Practice</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>s=int(input())
+if s&gt;=90: print("A")
+elif s&gt;=75: print("B")
+elif s&gt;=50: print("C")
+else: print("Needs Practice")</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Login Role</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Login Role. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Role
+- Line 2: active/inactive
+### Output Format
+```
+Full Access
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>control-flow</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>nested-conditions</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>admin
+active</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Full Access</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>admin
+inactive</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>No Access</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>student
+active</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Learning Access</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>student
+inactive</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>No Access</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>guest
+active</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Limited Access</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>mentor
+active</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Limited Access</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>guest
+inactive</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>No Access</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>role=input()
+status=input()
+if status=="active":
+    if role=="admin": print("Full Access")
+    elif role=="student": print("Learning Access")
+    else: print("Limited Access")
+else: print("No Access")</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Day Code Type</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Day Code Type. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Code
+### Output Format
+```
+Weekday
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>control-flow</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>match-case</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>MON</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Weekday</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Weekend</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>SUN</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Weekend</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>FRI</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Weekday</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>TUE</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Weekday</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>code=input()
+if code in ("SAT","SUN"): print("Weekend")
+elif code in ("MON","TUE","WED","THU","FRI"): print("Weekday")
+else: print("Unknown")</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Python - Loan Eligibility Check</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>A bank approves a personal loan only after checking the applicant's age first, and only checks their income if the age requirement is met. Write a program that reads an applicant's age and monthly income, then prints the loan decision: 'Rejected: Age' if the applicant is under 21, 'Rejected: Income' if they are old enough but earn less than 20000, and 'Approved' otherwise.
 ### Input Format
@@ -4181,136 +6103,148 @@
 ```
 Approved
 ```
+### Example Walkthrough
+In the sample, the age is `25` and the income is `30000`. Since the age clears `21` and the income clears `20000`, the program prints `Approved`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>if-else</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>nested-conditions</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O25" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P25" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q25" t="b">
-        <v>1</v>
-      </c>
-      <c r="R25" t="inlineStr">
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>25
 30000</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>19
 50000</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Rejected: Age</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>30
 15000</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Rejected: Income</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>21
 20000</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>20
 99999</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Rejected: Age</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>21
 19999</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>Rejected: Income</t>
         </is>
       </c>
-      <c r="AD25" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>50
 100000</t>
         </is>
       </c>
-      <c r="AE25" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AG25" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>age = int(input())
 income = float(input())
@@ -4324,13 +6258,13 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Guarded Withdrawal Validation</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>An ATM's validation logic checks the most obvious failure cases first, before checking anything else, so that clearer error messages are shown earlier. Write a program that reads an account balance and a withdrawal amount, then prints 'Invalid Amount' if the amount is zero or negative, 'Insufficient Funds' if the amount is positive but exceeds the balance, and 'Approved' otherwise.
 ### Input Format
@@ -4340,136 +6274,148 @@
 ```
 Approved
 ```
+### Example Walkthrough
+In the sample, the balance is `5000` and the requested amount is `2000`. The amount is positive and does not exceed the balance, so the program prints `Approved`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>if-else</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>conditional-statements</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O26" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P26" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q26" t="b">
-        <v>1</v>
-      </c>
-      <c r="R26" t="inlineStr">
+      <c r="P3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>5000
 1000</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>5000
 -200</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Invalid Amount</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>500
 800</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Insufficient Funds</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>500
 0</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Invalid Amount</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>500
 500</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>500
 501</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>Insufficient Funds</t>
         </is>
       </c>
-      <c r="AD26" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>500
 -5</t>
         </is>
       </c>
-      <c r="AE26" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>Invalid Amount</t>
         </is>
       </c>
-      <c r="AG26" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>balance = float(input())
 amount = float(input())
@@ -4482,13 +6428,13 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Nested Membership Discount Eligibility</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>A store's loyalty programme gives different discounts depending on both the customer's membership tier and their purchase amount. Write a program that reads a membership tier as the text 'Gold' or 'Silver' and a purchase amount, then prints the discount percentage: a Gold member gets 20 percent if the purchase is at least 2000, otherwise 10 percent; a Silver member gets 10 percent if the purchase is at least 2000, otherwise 5 percent.
 ### Input Format
@@ -4496,138 +6442,150 @@
 - Line 2: Purchase amount
 ### Output Format
 ```
-Discount: &lt;discount&gt;%
-```
+Discount: 20%
+```
+### Example Walkthrough
+In the sample, the tier is `Gold` and the purchase is `2500`. Since the tier is Gold and the amount is at least `2000`, the discount is `20` percent, so the program prints `Discount: 20%`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>if-else</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>nested-conditions</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O27" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P27" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q27" t="b">
-        <v>1</v>
-      </c>
-      <c r="R27" t="inlineStr">
+      <c r="P4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>Gold
 2500</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Discount: 20%</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Gold
 1000</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Discount: 10%</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Silver
 3000</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Discount: 10%</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>Gold
 1999</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Discount: 10%</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>Silver
 1999</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Discount: 5%</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>Silver
 2000</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>Discount: 10%</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>Gold
 0</t>
         </is>
       </c>
-      <c r="AE27" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>Discount: 10%</t>
         </is>
       </c>
-      <c r="AG27" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>tier = input()
 amount = float(input())
@@ -4645,13 +6603,13 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Grade with Attendance Override</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>A college's grading policy first computes the marks-based grade, but caps any grade at 'C' if the student's attendance was below 75 percent, regardless of how high their marks were. Write a program that reads a student's marks and attendance percentage, then prints the final grade following this policy, using the usual marks bands: 'A' for 90 or above, 'B' for 75 up to 90, 'C' for 60 up to 75, and 'F' below 60.
 ### Input Format
@@ -4661,136 +6619,148 @@
 ```
 B
 ```
+### Example Walkthrough
+In the sample, the marks are `80` and the attendance is `85`. The marks-based grade is `B` (`75` up to `90`), and since attendance is at least `75`, no override applies, so the program prints `B`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>if-else</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>nested-conditions</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O28" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P28" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q28" t="b">
-        <v>1</v>
-      </c>
-      <c r="R28" t="inlineStr">
+      <c r="P5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>95
 80</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>95
 50</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>45
 50</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>74.9
 90</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>90
 74.9</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>30
 50</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="AD28" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>75
 75</t>
         </is>
       </c>
-      <c r="AE28" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="AG28" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>marks = float(input())
 attendance = float(input())
@@ -4808,13 +6778,13 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Tiered Speeding Fine Calculator</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Traffic police calculate a fine based on how far over the speed limit a vehicle was travelling. Write a program that reads a vehicle's speed and the road's speed limit, then prints the fine: 0 if the vehicle was at or under the limit, 500 if it exceeded the limit by up to 20, and 1500 if it exceeded the limit by more than 20.
 ### Input Format
@@ -4822,138 +6792,150 @@
 - Line 2: Speed limit
 ### Output Format
 ```
-Fine: &lt;fine&gt;
-```
+Fine: 1500
+```
+### Example Walkthrough
+In the sample, the speed is `90` against a limit of `60`, so the vehicle is `30` over. Since `30` is more than `20` over the limit, the fine is `1500`, and the program prints `Fine: 1500`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>if-else</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>conditional-statements</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O29" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q29" t="b">
-        <v>1</v>
-      </c>
-      <c r="R29" t="inlineStr">
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>60
 60</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>Fine: 0</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>75
 60</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Fine: 500</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>100
 60</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Fine: 1500</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>59
 60</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Fine: 0</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>80
 60</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Fine: 500</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>81
 60</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>Fine: 1500</t>
         </is>
       </c>
-      <c r="AD29" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="AE29" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>Fine: 0</t>
         </is>
       </c>
-      <c r="AG29" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>speed = float(input())
 limit = float(input())
@@ -4968,13 +6950,13 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Parity and Sign Combined</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>A number-classifier tool labels a number by both its sign and its parity in one combined word. Write a program that reads an integer and prints one of 'Positive Even', 'Positive Odd', 'Negative Even', 'Negative Odd', or 'Zero', using ternary (conditional) expressions rather than full if-else blocks.
 ### Input Format
@@ -4983,129 +6965,141 @@
 ```
 Positive Even
 ```
+### Example Walkthrough
+In the sample, the number is `8`. It is greater than `0`, so the sign is `Positive`, and since `8 % 2 == 0`, it is `Even`, so the program prints `Positive Even`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>if-else</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>conditional-expressions</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O30" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P30" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q30" t="b">
-        <v>1</v>
-      </c>
-      <c r="R30" t="inlineStr">
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>Positive Even</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Negative Odd</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Zero</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Negative Even</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Positive Odd</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>Positive Even</t>
         </is>
       </c>
-      <c r="AD30" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="AE30" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>Negative Odd</t>
         </is>
       </c>
-      <c r="AG30" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>n = int(input())
 sign = "Zero" if n == 0 else ("Positive" if n &gt; 0 else "Negative")
@@ -5114,13 +7108,13 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Insurance Claim Approval</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>An insurance company auto-approves small claims with valid policies, refers large claims for manual review, and rejects anything from an inactive policy outright. Write a program that reads whether the policy is active (1 for yes, 0 for no) and the claim amount, then prints the decision: 'Rejected: Inactive Policy' if the policy is inactive; otherwise, for an active policy, 'Auto Approved' if the claim is at most 10000, and 'Manual Review' if it is more than 10000.
 ### Input Format
@@ -5130,136 +7124,148 @@
 ```
 Auto Approved
 ```
+### Example Walkthrough
+In the sample, the policy is active (`1`) and the claim is `5000`. Since the policy is active and the claim is at most `10000`, the program prints `Auto Approved`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>if-else</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>nested-conditions</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O31" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P31" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q31" t="b">
-        <v>1</v>
-      </c>
-      <c r="R31" t="inlineStr">
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>1
 5000</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>Auto Approved</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>0
 5000</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Rejected: Inactive Policy</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>1
 25000</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Manual Review</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>0
 1</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Rejected: Inactive Policy</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>1
 10000</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Auto Approved</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>1
 10001</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>Manual Review</t>
         </is>
       </c>
-      <c r="AD31" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>0
 999999</t>
         </is>
       </c>
-      <c r="AE31" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>Rejected: Inactive Policy</t>
         </is>
       </c>
-      <c r="AG31" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>is_active = int(input())
 claim_amount = float(input())
@@ -5273,6 +7279,507 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Python - Scholarship Check</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Scholarship Check. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Marks
+- Line 2: Attendance
+### Output Format
+```
+Eligible
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>control-flow</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>nested-conditions</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>90
+95</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Eligible</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>85
+89</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Waitlist</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>80
+95</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Waitlist</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>70
+80</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>99
+90</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Eligible</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>85
+90</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Eligible</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>84
+89</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>m=int(input())
+a=int(input())
+if m&gt;=85 and a&gt;=90: print("Eligible")
+elif m&gt;=85 or a&gt;=90: print("Waitlist")
+else: print("Not Eligible")</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Triangle Type</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Triangle Type. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: a
+- Line 2: b
+- Line 3: c
+### Output Format
+```
+Equilateral
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>control-flow</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>conditional-statements</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>3
+3
+3</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Equilateral</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>3
+3
+4</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Isosceles</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>3
+4
+5</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Scalene</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>1
+2
+3</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>5
+1
+1</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>0
+1
+1</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>10
+6
+6</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>Isosceles</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>a=int(input()); b=int(input()); c=int(input())
+if a+b&lt;=c or a+c&lt;=b or b+c&lt;=a or a&lt;=0 or b&lt;=0 or c&lt;=0: print("Invalid")
+elif a==b==c: print("Equilateral")
+elif a==b or b==c or a==c: print("Isosceles")
+else: print("Scalene")</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Safe Division Decision</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Safe Division Decision. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Numerator
+- Line 2: Divisor
+### Output Format
+```
+5.0
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>control-flow</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>input-validation</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>10
+2</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>5
+0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Cannot divide</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0
+5</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>7
+2</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>-6
+3</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>6
+-3</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>1
+4</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>a=float(input())
+b=float(input())
+print("Cannot divide" if b==0 else a/b)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content/Question Bank/Coding Questions/Unit 3 - Control Flow/Unit 3 - Control Flow - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 3 - Control Flow/Unit 3 - Control Flow - Coding Questions.xlsx
@@ -1913,16 +1913,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Even Entry Check. Read the input values and print the required result exactly.
+          <t>A community lucky-draw booth uses locker token numbers to decide who gets to enter the bonus round - only even-numbered tokens qualify. Write a program that reads a token number and prints whether it is eligible. Print `Eligible` if the number is even, and `Not Eligible` if it is odd.
 ### Input Format
-- Line 1: Token
+- Line 1: Token number
 ### Output Format
 ```
 Eligible
 ```
+### Example Walkthrough
+In the sample, the token number is `2`. Since `2 % 2 == 0`, the number is even, so the program prints `Eligible`. A token number of `3` would instead print `Not Eligible`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid integers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -2067,16 +2069,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Pass Fail Label. Read the input values and print the required result exactly.
+          <t>A skills-certification platform scores every attempt and needs to instantly label it before generating the certificate. Any score of 40 or above counts as a passing attempt. Write a program that reads an attempt's score and prints exactly `Pass` if the score is 40 or more, and exactly `Fail` otherwise.
 ### Input Format
 - Line 1: Score
 ### Output Format
 ```
 Pass
 ```
+### Example Walkthrough
+In the sample, the score is `40`. Since `40 &gt;= 40`, the passing condition is true, so the program prints `Pass`. A score of `39` would instead print `Fail`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -3715,16 +3719,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Temperature Alert. Read the input values and print the required result exactly.
+          <t>A weather-monitoring app sends out a heat alert whenever the recorded temperature crosses a safe threshold. Write a program that reads a temperature reading (in Celsius) and prints whether it should trigger a heat alert. Print `Hot` if the temperature is strictly greater than 35, and `Normal` otherwise.
 ### Input Format
 - Line 1: Temperature
 ### Output Format
 ```
 Hot
 ```
+### Example Walkthrough
+In the sample, the temperature is `36`. Since `36 &gt; 35`, the program prints `Hot`. A temperature of `35` would instead print `Normal`, since it does not exceed the threshold.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -3869,17 +3875,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Largest of Two. Read the input values and print the required result exactly.
+          <t>A quick scoreboard widget compares two submitted values and highlights the larger one. Write a program that reads two numbers and prints the larger of the two. If the two numbers are equal, print that common value.
 ### Input Format
-- Line 1: First
-- Line 2: Second
+- Line 1: First number
+- Line 2: Second number
 ### Output Format
 ```
 5
 ```
+### Example Walkthrough
+In the sample, the first number is `5` and the second is `3`. Since `5` is greater than `3`, the program prints `5`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid integers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -5429,16 +5437,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Grade Band. Read the input values and print the required result exactly.
+          <t>An online course dashboard sorts learners into performance bands based on their quiz score, so instructors know who needs extra help. Write a program that reads a score and prints the grade band: `A` for scores of 90 or above, `B` for scores from 75 up to (but not including) 90, `C` for scores from 50 up to (but not including) 75, and `Needs Practice` for anything below 50.
 ### Input Format
 - Line 1: Score
 ### Output Format
 ```
 A
 ```
+### Example Walkthrough
+In the sample, the score is `95`. Since `95` is 90 or above, the program prints `A`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -5586,17 +5596,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Login Role. Read the input values and print the required result exactly.
+          <t>A campus portal grants different levels of access depending on a user's role and whether their account is currently active. Write a program that reads a role and an account status (`active` or `inactive`), then prints the access level. If the account is inactive, print `No Access` regardless of role. If the account is active: print `Full Access` for role `admin`, `Learning Access` for role `student`, and `Limited Access` for any other role.
 ### Input Format
 - Line 1: Role
-- Line 2: active/inactive
+- Line 2: Account status (`active` or `inactive`)
 ### Output Format
 ```
 Full Access
 ```
+### Example Walkthrough
+In the sample, the role is `admin` and the status is `active`. Since the account is active and the role is `admin`, the program prints `Full Access`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All inputs follow the exact casing and format shown in the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -5753,16 +5765,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Day Code Type. Read the input values and print the required result exactly.
+          <t>A scheduling system tags each day code coming from an upstream system as a weekday or weekend slot before assigning shifts. Write a program that reads a three-letter day code and prints its type. Print `Weekend` for `SAT` or `SUN`, `Weekday` for `MON`, `TUE`, `WED`, `THU`, or `FRI`, and `Unknown` for any other code (the check is case-sensitive, so a lowercase code like `sat` also counts as `Unknown`).
 ### Input Format
-- Line 1: Code
+- Line 1: Day code
 ### Output Format
 ```
 Weekday
 ```
+### Example Walkthrough
+In the sample, the day code is `MON`. Since `MON` is one of the weekday codes, the program prints `Weekday`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- Day codes are provided in uppercase unless intentionally testing the Unknown case.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -7287,17 +7301,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Scholarship Check. Read the input values and print the required result exactly.
+          <t>A university scholarship committee screens applicants using both their marks and attendance before deciding who qualifies outright, who goes on a waitlist, and who is turned down. Write a program that reads a student's marks and attendance percentage, then prints the decision. Print `Eligible` if marks are 85 or above AND attendance is 90 or above; print `Waitlist` if only one of those two conditions is met; print `Not Eligible` if neither condition is met.
 ### Input Format
 - Line 1: Marks
-- Line 2: Attendance
+- Line 2: Attendance percentage
 ### Output Format
 ```
 Eligible
 ```
+### Example Walkthrough
+In the sample, the marks are `90` and the attendance is `95`. Since both marks (`&gt;= 85`) and attendance (`&gt;= 90`) meet the thresholds, the program prints `Eligible`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -7452,18 +7468,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Triangle Type. Read the input values and print the required result exactly.
+          <t>A geometry teaching tool checks three submitted side lengths and classifies the resulting shape, but first it must confirm the sides can actually form a triangle. Write a program that reads three side lengths a, b, and c, then prints the triangle type. Print `Invalid` if any side is zero or negative, or if the triangle inequality fails (the sum of any two sides is not strictly greater than the third). Otherwise, print `Equilateral` if all three sides are equal, `Isosceles` if exactly two sides are equal, and `Scalene` if all three sides are different.
 ### Input Format
-- Line 1: a
-- Line 2: b
-- Line 3: c
+- Line 1: Side a
+- Line 2: Side b
+- Line 3: Side c
 ### Output Format
 ```
 Equilateral
 ```
+### Example Walkthrough
+In the sample, the sides are `3`, `3`, and `3`. They satisfy the triangle inequality, and all three sides are equal, so the program prints `Equilateral`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid integers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -7625,7 +7643,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Safe Division Decision. Read the input values and print the required result exactly.
+          <t>A calculator utility divides two numbers submitted by a user, but must guard against a divide-by-zero crash. Write a program that reads a numerator and a divisor, then prints the result. If the divisor is 0, print `Cannot divide`; otherwise print the numerator divided by the divisor as a floating-point value.
 ### Input Format
 - Line 1: Numerator
 - Line 2: Divisor
@@ -7633,9 +7651,11 @@
 ```
 5.0
 ```
+### Example Walkthrough
+In the sample, the numerator is `10` and the divisor is `2`. Since the divisor is not `0`, the program prints `10 / 2`, which is `5.0`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">

--- a/content/Question Bank/Coding Questions/Unit 3 - Control Flow/Unit 3 - Control Flow - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 3 - Control Flow/Unit 3 - Control Flow - Coding Questions.xlsx
@@ -1913,7 +1913,8 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A community lucky-draw booth uses locker token numbers to decide who gets to enter the bonus round - only even-numbered tokens qualify. Write a program that reads a token number and prints whether it is eligible. Print `Eligible` if the number is even, and `Not Eligible` if it is odd.
+          <t>A lucky-draw counter at a college fest only lets in visitors whose token number is even, since odd tokens go to a different queue.
+Write a program that reads a visitor's token number and prints `Eligible` if the number is even, and `Not Eligible` otherwise.
 ### Input Format
 - Line 1: Token number
 ### Output Format
@@ -1921,9 +1922,9 @@
 Eligible
 ```
 ### Example Walkthrough
-In the sample, the token number is `2`. Since `2 % 2 == 0`, the number is even, so the program prints `Eligible`. A token number of `3` would instead print `Not Eligible`.
+In the sample, the token is 2. Since 2 is divisible by 2 with no remainder, it is even, so the program prints `Eligible`. A token of 3 would instead print `Not Eligible`.
 ### Constraints
-- All numeric inputs are valid integers in the ranges implied by the examples.
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -2069,7 +2070,8 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A skills-certification platform scores every attempt and needs to instantly label it before generating the certificate. Any score of 40 or above counts as a passing attempt. Write a program that reads an attempt's score and prints exactly `Pass` if the score is 40 or more, and exactly `Fail` otherwise.
+          <t>A results portal needs to instantly label each student's score as a pass or a fail the moment it is entered, before the full report card is generated. The passing cutoff is a score of 40 or more.
+Write a program that reads a student's score and prints `Pass` if the score is 40 or more, and `Fail` otherwise.
 ### Input Format
 - Line 1: Score
 ### Output Format
@@ -2077,9 +2079,9 @@
 Pass
 ```
 ### Example Walkthrough
-In the sample, the score is `40`. Since `40 &gt;= 40`, the passing condition is true, so the program prints `Pass`. A score of `39` would instead print `Fail`.
+In the sample, the score is 40. Since 40 is greater than or equal to 40, the program prints `Pass`. A score of 39 would instead print `Fail`.
 ### Constraints
-- All numeric inputs are valid numbers in the ranges implied by the examples.
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -3719,7 +3721,8 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A weather-monitoring app sends out a heat alert whenever the recorded temperature crosses a safe threshold. Write a program that reads a temperature reading (in Celsius) and prints whether it should trigger a heat alert. Print `Hot` if the temperature is strictly greater than 35, and `Normal` otherwise.
+          <t>A weather station's alert board flashes a warning whenever the recorded temperature crosses into dangerously hot territory, defined as anything above 35 degrees.
+Write a program that reads the current temperature as a decimal number and prints `Hot` if it is strictly greater than 35, and `Normal` otherwise.
 ### Input Format
 - Line 1: Temperature
 ### Output Format
@@ -3727,7 +3730,7 @@
 Hot
 ```
 ### Example Walkthrough
-In the sample, the temperature is `36`. Since `36 &gt; 35`, the program prints `Hot`. A temperature of `35` would instead print `Normal`, since it does not exceed the threshold.
+In the sample, the temperature is 36. Since 36 is greater than 35, the program prints `Hot`. A temperature of exactly 35 would instead print `Normal`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -3875,18 +3878,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A quick scoreboard widget compares two submitted values and highlights the larger one. Write a program that reads two numbers and prints the larger of the two. If the two numbers are equal, print that common value.
+          <t>A scoreboard app compares two contestants' scores after every round and highlights whichever one is ahead, breaking ties in favor of the first contestant.
+Write a program that reads two scores and prints the larger of the two; if they are equal, print the first score.
 ### Input Format
-- Line 1: First number
-- Line 2: Second number
+- Line 1: First score
+- Line 2: Second score
 ### Output Format
 ```
 5
 ```
 ### Example Walkthrough
-In the sample, the first number is `5` and the second is `3`. Since `5` is greater than `3`, the program prints `5`.
+In the sample, the first score is 5 and the second is 3. Since 5 is greater than or equal to 3, the program prints `5`.
 ### Constraints
-- All numeric inputs are valid integers in the ranges implied by the examples.
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -5437,7 +5441,8 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>An online course dashboard sorts learners into performance bands based on their quiz score, so instructors know who needs extra help. Write a program that reads a score and prints the grade band: `A` for scores of 90 or above, `B` for scores from 75 up to (but not including) 90, `C` for scores from 50 up to (but not including) 75, and `Needs Practice` for anything below 50.
+          <t>A results portal converts every numeric score into a letter grade band before displaying it on the student dashboard. The bands are: 90 or above is `A`, 75 up to 89 is `B`, 50 up to 74 is `C`, and anything below 50 is `Needs Practice`.
+Write a program that reads a student's score and prints the correct grade band using these cutoffs.
 ### Input Format
 - Line 1: Score
 ### Output Format
@@ -5445,9 +5450,9 @@
 A
 ```
 ### Example Walkthrough
-In the sample, the score is `95`. Since `95` is 90 or above, the program prints `A`.
+In the sample, the score is 95. Since 95 is 90 or above, the program prints `A`. A score of 80 would print `B`, 65 would print `C`, and 40 would print `Needs Practice`.
 ### Constraints
-- All numeric inputs are valid numbers in the ranges implied by the examples.
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -5596,18 +5601,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A campus portal grants different levels of access depending on a user's role and whether their account is currently active. Write a program that reads a role and an account status (`active` or `inactive`), then prints the access level. If the account is inactive, print `No Access` regardless of role. If the account is active: print `Full Access` for role `admin`, `Learning Access` for role `student`, and `Limited Access` for any other role.
+          <t>A campus portal decides what a logged-in user can see based on two things: their account status and their role. If the account is not `active`, the user gets no access regardless of role. If it is active, an `admin` gets full access, a `student` gets learning access, and anyone else gets limited access.
+Write a program that reads the role and the status, then prints exactly one of `Full Access`, `Learning Access`, `Limited Access`, or `No Access` following this rule.
 ### Input Format
 - Line 1: Role
-- Line 2: Account status (`active` or `inactive`)
+- Line 2: Status (`active` or any other value)
 ### Output Format
 ```
 Full Access
 ```
 ### Example Walkthrough
-In the sample, the role is `admin` and the status is `active`. Since the account is active and the role is `admin`, the program prints `Full Access`.
+In the sample, the role is admin and the status is active. Since the status is active and the role is admin, the program prints `Full Access`.
 ### Constraints
-- All inputs follow the exact casing and format shown in the examples.
+- Role and status are valid strings with no leading or trailing spaces.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -5765,7 +5771,8 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A scheduling system tags each day code coming from an upstream system as a weekday or weekend slot before assigning shifts. Write a program that reads a three-letter day code and prints its type. Print `Weekend` for `SAT` or `SUN`, `Weekday` for `MON`, `TUE`, `WED`, `THU`, or `FRI`, and `Unknown` for any other code (the check is case-sensitive, so a lowercase code like `sat` also counts as `Unknown`).
+          <t>A hostel mess planning tool reads a three-letter day code and needs to know whether it falls on a weekday or a weekend, so it can plan the right menu. `SAT` and `SUN` are weekends, `MON` through `FRI` are weekdays, and anything else is not a recognized code.
+Write a program that reads a three-letter day code and prints `Weekend`, `Weekday`, or `Unknown` accordingly. The check is case-sensitive.
 ### Input Format
 - Line 1: Day code
 ### Output Format
@@ -5773,9 +5780,9 @@
 Weekday
 ```
 ### Example Walkthrough
-In the sample, the day code is `MON`. Since `MON` is one of the weekday codes, the program prints `Weekday`.
+In the sample, the code is MON. Since MON is one of the weekday codes, the program prints `Weekday`. A code of SAT would print `Weekend`, and a lowercase code like sat would print `Unknown` since the check is case-sensitive.
 ### Constraints
-- Day codes are provided in uppercase unless intentionally testing the Unknown case.
+- Day code is a valid string with no leading or trailing spaces.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -7301,18 +7308,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A university scholarship committee screens applicants using both their marks and attendance before deciding who qualifies outright, who goes on a waitlist, and who is turned down. Write a program that reads a student's marks and attendance percentage, then prints the decision. Print `Eligible` if marks are 85 or above AND attendance is 90 or above; print `Waitlist` if only one of those two conditions is met; print `Not Eligible` if neither condition is met.
+          <t>A scholarship committee reviews each applicant's marks percentage and attendance percentage together. An applicant is fully `Eligible` only when both marks are at least 85 and attendance is at least 90; if only one of the two conditions is met they go on a `Waitlist`; if neither is met they are `Not Eligible`.
+Write a program that reads the marks percentage and the attendance percentage, then prints `Eligible`, `Waitlist`, or `Not Eligible` following this rule.
 ### Input Format
-- Line 1: Marks
+- Line 1: Marks percentage
 - Line 2: Attendance percentage
 ### Output Format
 ```
 Eligible
 ```
 ### Example Walkthrough
-In the sample, the marks are `90` and the attendance is `95`. Since both marks (`&gt;= 85`) and attendance (`&gt;= 90`) meet the thresholds, the program prints `Eligible`.
+In the sample, marks are 90 and attendance is 95. Since marks are at least 85 and attendance is at least 90, both conditions are met, so the program prints `Eligible`. Marks of 85 with attendance of 89 would meet only one condition and print `Waitlist`.
 ### Constraints
-- All numeric inputs are valid numbers in the ranges implied by the examples.
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -7468,7 +7476,8 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A geometry teaching tool checks three submitted side lengths and classifies the resulting shape, but first it must confirm the sides can actually form a triangle. Write a program that reads three side lengths a, b, and c, then prints the triangle type. Print `Invalid` if any side is zero or negative, or if the triangle inequality fails (the sum of any two sides is not strictly greater than the third). Otherwise, print `Equilateral` if all three sides are equal, `Isosceles` if exactly two sides are equal, and `Scalene` if all three sides are different.
+          <t>A geometry teaching app checks three side lengths entered by a student and classifies the shape before drawing it. The sides must each be positive and satisfy the triangle inequality (no side can be greater than or equal to the sum of the other two), otherwise the shape is `Invalid`. A valid triangle with all three sides equal is `Equilateral`, one with exactly two equal sides is `Isosceles`, and one with all different sides is `Scalene`.
+Write a program that reads three side lengths and prints `Invalid`, `Equilateral`, `Isosceles`, or `Scalene` following this rule.
 ### Input Format
 - Line 1: Side a
 - Line 2: Side b
@@ -7478,9 +7487,9 @@
 Equilateral
 ```
 ### Example Walkthrough
-In the sample, the sides are `3`, `3`, and `3`. They satisfy the triangle inequality, and all three sides are equal, so the program prints `Equilateral`.
+In the sample, the sides are 3, 3, and 3. They form a valid triangle and all three sides are equal, so the program prints `Equilateral`. Sides 3, 3, 4 would print `Isosceles`, and sides 1, 2, 3 would print `Invalid` since 1 + 2 is not greater than 3.
 ### Constraints
-- All numeric inputs are valid integers in the ranges implied by the examples.
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -7643,16 +7652,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A calculator utility divides two numbers submitted by a user, but must guard against a divide-by-zero crash. Write a program that reads a numerator and a divisor, then prints the result. If the divisor is 0, print `Cannot divide`; otherwise print the numerator divided by the divisor as a floating-point value.
+          <t>A calculator widget divides two numbers a user enters, but must guard against a zero denominator instead of letting the app crash.
+Write a program that reads two decimal numbers and prints their quotient (first divided by second); if the second number is 0, print `Cannot divide` instead.
 ### Input Format
-- Line 1: Numerator
-- Line 2: Divisor
+- Line 1: First number
+- Line 2: Second number
 ### Output Format
 ```
 5.0
 ```
 ### Example Walkthrough
-In the sample, the numerator is `10` and the divisor is `2`. Since the divisor is not `0`, the program prints `10 / 2`, which is `5.0`.
+In the sample, the numbers are 10 and 2. Since 2 is not 0, the program divides 10 by 2 and prints `5.0`. If the second number were 0, it would print `Cannot divide` instead.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>

--- a/content/Question Bank/Coding Questions/Unit 3 - Control Flow/Unit 3 - Control Flow - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 3 - Control Flow/Unit 3 - Control Flow - Coding Questions.xlsx
@@ -7,10 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - Coding - Unit 3" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH11"/>
+  <dimension ref="A1:AH41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,17 +598,11 @@
         <is>
           <t>Results are out, and the exam hall coordinator has a long list of marks to sort into pass and fail before the revaluation window opens. The university's rule is simple: 40 marks or more is a pass.
 Write a program that reads a student's marks and prints exactly `Pass` if the marks are 40 or more, and exactly `Fail` otherwise.
-### Input Format
-- Line 1: Marks
-### Output Format
-```
-Pass
-```
 ### Example Walkthrough
 In the sample, the marks are 55. Since 55 is greater than or equal to 40, the passing condition is true, so the program prints `Pass`. Marks of 39 would instead print `Fail`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -743,8 +734,8 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>marks = float(input())
-if marks &gt;= 40:
+          <t>marks = float(input())  # read the student's marks
+if marks &gt;= 40:            # 40 is the minimum passing mark
     print("Pass")
 else:
     print("Fail")</t>
@@ -761,17 +752,11 @@
         <is>
           <t>The campus gym has two rows of lockers: even-numbered lockers along the left wall and odd-numbered ones along the right. When a student is assigned a locker, the app must tell them which row to walk to.
 Write a program that reads a locker number and prints `Even` if the number is even and `Odd` if it is odd. A number is even when dividing it by 2 leaves no remainder - that is, nothing is left over.
-### Input Format
-- Line 1: Locker number
-### Output Format
-```
-Even
-```
 ### Example Walkthrough
 In the sample, the locker number is 24. Dividing 24 by 2 leaves a remainder of 0, so the number is even and the program prints `Even`. A locker like 7 leaves a remainder of 1, so it would print `Odd`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -903,8 +888,8 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>locker = int(input())
-if locker % 2 == 0:
+          <t>locker = int(input())  # read the locker number
+if locker % 2 == 0:    # remainder 0 means the number is even
     print("Even")
 else:
     print("Odd")</t>
@@ -921,17 +906,11 @@
         <is>
           <t>It is election season, and volunteers at the local helpdesk answer one question all day: "Am I old enough to vote?" In India the answer depends on a single number - you must be at least 18.
 Write a program that reads a citizen's age and prints exactly `Eligible to vote` if the age is 18 or more, and exactly `Not eligible to vote` otherwise.
-### Input Format
-- Line 1: Age
-### Output Format
-```
-Eligible to vote
-```
 ### Example Walkthrough
 In the sample, the age is 19. Since 19 is at least 18, the condition is satisfied and the program prints `Eligible to vote`. An age of 17 would print `Not eligible to vote` instead.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1063,8 +1042,8 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>age = int(input())
-if age &gt;= 18:
+          <t>age = int(input())  # read the person's age
+if age &gt;= 18:                   # 18 is the minimum voting age
     print("Eligible to vote")
 else:
     print("Not eligible to vote")</t>
@@ -1081,17 +1060,11 @@
         <is>
           <t>During its monsoon sale, an online store gives a discount to anyone whose cart total reaches Rs.1000. As shoppers keep adding items, the cart page keeps checking whether they have crossed the line.
 Write a program that reads the cart total and prints exactly `Eligible for discount` if the total is 1000 or more, and exactly `No discount` otherwise.
-### Input Format
-- Line 1: Cart total
-### Output Format
-```
-Eligible for discount
-```
 ### Example Walkthrough
 In the sample, the cart total is 1500. Since 1500 is at least 1000, the shopper qualifies and the program prints `Eligible for discount`. A total of 750 would print `No discount`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1223,8 +1196,8 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>cart_total = float(input())
-if cart_total &gt;= 1000:
+          <t>cart_total = float(input())  # read the cart's total value
+if cart_total &gt;= 1000:             # discount kicks in at this threshold
     print("Eligible for discount")
 else:
     print("No discount")</t>
@@ -1241,18 +1214,11 @@
         <is>
           <t>The report card generator at a college assigns letter grades from marks, but there is a catch: a student with poor attendance cannot get a good grade no matter how well they scored. The attendance check is applied first, before marks are even looked at.
 Write a program that reads a student's marks and attendance percentage. If the attendance is below 75, print `D` regardless of the marks. Otherwise grade by marks: `A` for 90 or above, `B` for 75 up to (but not including) 90, `C` for 60 up to (but not including) 75, and `D` below 60.
-### Input Format
-- Line 1: Marks
-- Line 2: Attendance percentage
-### Output Format
-```
-D
-```
 ### Example Walkthrough
 In the sample, the marks are 95 and the attendance is 60. Because 60 is below 75, the attendance rule kicks in first and caps the grade, so the program prints `D` - even though 95 marks would normally earn an `A`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1393,7 +1359,7 @@
         <is>
           <t>marks = float(input())
 attendance_percentage = float(input())
-if attendance_percentage &lt; 75:
+if attendance_percentage &lt; 75:   # low attendance overrides the marks-based grade
     grade = 'D'
 elif marks &gt;= 90:
     grade = 'A'
@@ -1402,7 +1368,7 @@
 elif marks &gt;= 60:
     grade = 'C'
 else:
-    grade = 'D'
+    grade = 'D'                  # falls through here whenever marks &lt; 60
 print(grade)</t>
         </is>
       </c>
@@ -1417,18 +1383,11 @@
         <is>
           <t>Sneha is at an ATM trying to withdraw cash. The machine approves a withdrawal only when two things are both true: her balance covers the amount, and the amount is a multiple of 100, because the machine only holds Rs.100 notes.
 Write a program that reads the account balance and the withdrawal amount, then prints exactly `Approved` if the amount is no more than the balance and is a multiple of 100 (dividing it by 100 leaves no remainder); otherwise print exactly `Denied`.
-### Input Format
-- Line 1: Account balance
-- Line 2: Withdrawal amount
-### Output Format
-```
-Approved
-```
 ### Example Walkthrough
 In the sample, the balance is 5000 and the request is 2000. First check: 2000 is not more than 5000, so the funds are sufficient. Second check: 2000 divided by 100 leaves no remainder, so it is a valid multiple. Both checks pass, and the program prints `Approved`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1569,7 +1528,7 @@
         <is>
           <t>balance = float(input())
 amount = float(input())
-if amount &lt;= balance and amount % 100 == 0:
+if amount &lt;= balance and amount % 100 == 0:  # enough funds and a multiple of 100
     print("Approved")
 else:
     print("Denied")</t>
@@ -1586,18 +1545,11 @@
         <is>
           <t>A cab app raises its fare multiplier during busy hours, and weekends behave differently from weekdays. Before showing the fare, the pricing engine looks at two things - what kind of day it is and what hour it is - and then picks the multiplier.
 Write a program that reads the day type (`weekday` or `weekend`) and the hour of the day (0-23), then prints the surge multiplier. Peak hours are 8 to 10 and 17 to 19 (inclusive on both ends). On weekends the surge is 2.0 during peak hours and 1.2 otherwise; on weekdays it is 1.5 during peak hours and 1.0 otherwise. Print the multiplier with exactly one digit after the decimal point.
-### Input Format
-- Line 1: Day type (`weekday` or `weekend`)
-- Line 2: Hour (0-23)
-### Output Format
-```
-1.5
-```
 ### Example Walkthrough
 In the sample, the day type is `weekday` and the hour is 9. Since 9 falls inside the morning peak window of 8 to 10, this is a weekday peak-hour ride, so the multiplier is 1.5 and the program prints `1.5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1738,12 +1690,12 @@
         <is>
           <t>day_type = input()
 hour = int(input())
-is_peak = (8 &lt;= hour &lt;= 10) or (17 &lt;= hour &lt;= 19)
+is_peak = (8 &lt;= hour &lt;= 10) or (17 &lt;= hour &lt;= 19)  # morning or evening rush hour
 if day_type == "weekend":
-    surge = 2.0 if is_peak else 1.2
+    surge = 2.0 if is_peak else 1.2   # weekend surge rates
 else:
-    surge = 1.5 if is_peak else 1.0
-print(f"{surge:.1f}")</t>
+    surge = 1.5 if is_peak else 1.0   # weekday surge rates
+print(f"{surge:.1f}")   # show the surge multiplier with one decimal place</t>
         </is>
       </c>
     </row>
@@ -1757,17 +1709,11 @@
         <is>
           <t>A quick-feedback kiosk outside the exam hall shows students a single word - Pass or Fail - the moment they enter their marks. The developer wants the check written in one line using Python's conditional (ternary) expression instead of a full `if-else` block.
 Write a program that reads a student's marks and prints exactly `Pass` if the marks are 40 or more, and exactly `Fail` otherwise, using a one-line conditional expression of the form: `result = "Pass" if marks &gt;= 40 else "Fail"`.
-### Input Format
-- Line 1: Marks
-### Output Format
-```
-Pass
-```
 ### Example Walkthrough
 In the sample, the marks are 72. The condition `72 &gt;= 40` is true, so the conditional expression picks `Pass` and the program prints it. Marks of 25 would make the condition false and print `Fail`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1900,7 +1846,7 @@
       <c r="AG9" t="inlineStr">
         <is>
           <t>marks = float(input())
-result = "Pass" if marks &gt;= 40 else "Fail"
+result = "Pass" if marks &gt;= 40 else "Fail"   # ternary shorthand for if/else
 print(result)</t>
         </is>
       </c>
@@ -1915,17 +1861,11 @@
         <is>
           <t>A lucky-draw counter at a college fest only lets in visitors whose token number is even, since odd tokens go to a different queue.
 Write a program that reads a visitor's token number and prints `Eligible` if the number is even, and `Not Eligible` otherwise.
-### Input Format
-- Line 1: Token number
-### Output Format
-```
-Eligible
-```
 ### Example Walkthrough
 In the sample, the token is 2. Since 2 is divisible by 2 with no remainder, it is even, so the program prints `Eligible`. A token of 3 would instead print `Not Eligible`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -2058,7 +1998,7 @@
       <c r="AG10" t="inlineStr">
         <is>
           <t>n=int(input())
-print("Eligible" if n%2==0 else "Not Eligible")</t>
+print("Eligible" if n%2==0 else "Not Eligible")   # ternary check for an even number</t>
         </is>
       </c>
     </row>
@@ -2072,17 +2012,11 @@
         <is>
           <t>A results portal needs to instantly label each student's score as a pass or a fail the moment it is entered, before the full report card is generated. The passing cutoff is a score of 40 or more.
 Write a program that reads a student's score and prints `Pass` if the score is 40 or more, and `Fail` otherwise.
-### Input Format
-- Line 1: Score
-### Output Format
-```
-Pass
-```
 ### Example Walkthrough
 In the sample, the score is 40. Since 40 is greater than or equal to 40, the program prints `Pass`. A score of 39 would instead print `Fail`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -2215,2350 +2149,1900 @@
       <c r="AG11" t="inlineStr">
         <is>
           <t>s=int(input())
-print("Pass" if s&gt;=40 else "Fail")</t>
+print("Pass" if s&gt;=40 else "Fail")   # ternary expression replaces if/else</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Python - Largest of Three Numbers</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Three teams have just submitted their scores at the college quiz finals, and the scoreboard must highlight the highest one. As practice with decision-making, the organisers want the comparison done with nested `if` statements - an `if` inside another `if` - rather than Python's built-in `max` function.
 Write a program that reads three numbers (read them as decimal numbers) and prints the largest one in the form `Largest: &lt;largest&gt;`.
-### Input Format
-- Line 1: First number
-- Line 2: Second number
-- Line 3: Third number
-### Output Format
-```
-Largest: 27.0
-```
 ### Example Walkthrough
 In the sample, the three numbers are 12, 27, and 19. Comparing the first two, 27 beats 12; comparing that winner with 19, 27 is still bigger. Since the numbers are read as decimals, the program prints `Largest: 27.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>nested-conditions</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O12" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="b">
+        <v>1</v>
+      </c>
+      <c r="R12" t="inlineStr">
         <is>
           <t>12
 27
 19</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>Largest: 27.0</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>5
 5
 5</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Largest: 5.0</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>100
 20
 300</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Largest: 300.0</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>1
 2
 3</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Largest: 3.0</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>3
 2
 1</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Largest: 3.0</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>2
 3
 1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>Largest: 3.0</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>-5
 -2
 -8</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>Largest: -2.0</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG12" t="inlineStr">
         <is>
           <t>a = float(input())
 b = float(input())
 c = float(input())
 if a &gt;= b:
     if a &gt;= c:
-        largest = a
+        largest = a         # a is at least as big as both b and c
     else:
-        largest = c
+        largest = c         # c beat a, and a was already &gt;= b
 else:
     if b &gt;= c:
-        largest = b
+        largest = b         # b beat a, and b is at least as big as c
     else:
-        largest = c
+        largest = c         # c beat both a and b
 print("Largest:", largest)</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Python - Multi-Condition Loan Approval</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>A loan officer at a bank follows a two-path rule for personal loans: a high earner is approved on income alone, while a moderate earner still qualifies if someone co-signs the loan with them. Every other application is rejected.
 Write a program that reads the applicant's monthly income and whether they have a co-signer (1 for yes, 0 for no). Print exactly `Approved` if the income is at least 50000, or if the income is at least 25000 and there is a co-signer; otherwise print exactly `Rejected`.
-### Input Format
-- Line 1: Monthly income
-- Line 2: Has co-signer (1 or 0)
-### Output Format
-```
-Approved
-```
 ### Example Walkthrough
 In the sample, the income is 60000 with no co-signer (0). The first path already succeeds because 60000 is at least 50000, so the missing co-signer does not matter and the program prints `Approved`. An income of 40000 with no co-signer would satisfy neither path and print `Rejected`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>truthiness-and-boolean-logic</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O13" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P13" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="b">
+        <v>1</v>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>60000
 0</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>30000
 1</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>20000
 1</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>50000
 1</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>25000
 1</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>24999
 1</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>40000
 0</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE13" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG13" t="inlineStr">
         <is>
           <t>income = float(input())
 has_cosigner = int(input())
-if income &gt;= 50000 or (income &gt;= 25000 and has_cosigner == 1):
+if income &gt;= 50000 or (income &gt;= 25000 and has_cosigner == 1):  # high income, or moderate income with a cosigner
     print("Approved")
 else:
     print("Rejected")</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Python - Login Access Check</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>A members-only portal checks a flag to decide whether to grant access. Write a program that reads whether the user is a member (1 for yes, 0 for no) and prints whether access is granted.
-### Input Format
-- Line 1: Is member (1 or 0)
-### Output Format
-```
-Access Granted
-```
 ### Example Walkthrough
 In the sample, the member flag is `1`. Since `is_member == 1` is `True`, the program prints `Access Granted`. A flag of `0` would print `Access Denied` instead.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>conditional-statements</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O14" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="b">
+        <v>1</v>
+      </c>
+      <c r="R14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>Access Granted</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Access Denied</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Access Granted</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>Access Granted</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>Access Denied</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>Access Granted</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE14" t="inlineStr">
         <is>
           <t>Access Denied</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AG14" t="inlineStr">
         <is>
           <t>is_member = int(input())
-if is_member == 1:
+if is_member == 1:        # 1 means an active member
     print("Access Granted")
 else:
     print("Access Denied")</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Python - Age-Based Movie Ticket</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>A cinema counter issues either a child or an adult ticket based on the customer's age. Write a program that reads a customer's age and prints which ticket type they should be issued, using 18 as the cutoff age for an adult ticket.
-### Input Format
-- Line 1: Age
-### Output Format
-```
-Adult Ticket
-```
 ### Example Walkthrough
 In the sample, the age is `25`. Since `25 &gt;= 18`, the program prints `Adult Ticket`. An age below `18` would print `Child Ticket` instead.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>conditional-statements</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O15" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P15" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="b">
+        <v>1</v>
+      </c>
+      <c r="R15" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>Adult Ticket</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Child Ticket</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Adult Ticket</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>Child Ticket</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>Adult Ticket</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>Child Ticket</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE15" t="inlineStr">
         <is>
           <t>Adult Ticket</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AG15" t="inlineStr">
         <is>
           <t>age = int(input())
-if age &gt;= 18:
+if age &gt;= 18:              # 18 marks the adult ticket cutoff
     print("Adult Ticket")
 else:
     print("Child Ticket")</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Python - Weather Umbrella Advice</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>A weather app gives a simple reminder based on whether it is currently raining. Write a program that reads whether it is raining (1 for yes, 0 for no) and prints the appropriate advice.
-### Input Format
-- Line 1: Is raining (1 or 0)
-### Output Format
-```
-Carry an umbrella
-```
 ### Example Walkthrough
 In the sample, the rain flag is `1`. Since `is_raining == 1` is `True`, the program prints `Carry an umbrella`. A flag of `0` would print `No umbrella needed` instead.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>conditional-statements</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O16" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P16" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="b">
+        <v>1</v>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>Carry an umbrella</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>No umbrella needed</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Carry an umbrella</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>No umbrella needed</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>Carry an umbrella</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>No umbrella needed</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE16" t="inlineStr">
         <is>
           <t>Carry an umbrella</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AG16" t="inlineStr">
         <is>
           <t>is_raining = int(input())
-if is_raining == 1:
+if is_raining == 1:     # 1 represents rain, 0 represents no rain
     print("Carry an umbrella")
 else:
     print("No umbrella needed")</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Python - Account Balance Status</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>A banking app labels an account as overdrawn if its balance has gone below zero. Write a program that reads an account balance and prints whether the account is overdrawn or in credit.
-### Input Format
-- Line 1: Account balance
-### Output Format
-```
-In Credit
-```
 ### Example Walkthrough
 In the sample, the balance is `1500`. Since `1500` is not less than `0`, the account is not overdrawn, so the program prints `In Credit`. A negative balance would print `Overdrawn` instead.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>conditional-statements</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O17" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P17" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="b">
+        <v>1</v>
+      </c>
+      <c r="R17" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>In Credit</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>-200</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Overdrawn</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>In Credit</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>-0.01</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>Overdrawn</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>In Credit</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>-9999</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>Overdrawn</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE17" t="inlineStr">
         <is>
           <t>In Credit</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AG17" t="inlineStr">
         <is>
           <t>balance = float(input())
-if balance &lt; 0:
+if balance &lt; 0:      # a negative balance means the account is overdrawn
     print("Overdrawn")
 else:
     print("In Credit")</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Python - Library Book Return Status</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>The library front desk checks how many days late a returned book is to flag overdue returns. Write a program that reads the number of days a book is late and prints whether it is overdue or on time.
-### Input Format
-- Line 1: Days late
-### Output Format
-```
-Overdue
-```
 ### Example Walkthrough
 In the sample, the book is `5` days late. Since `5 &gt; 0`, the program prints `Overdue`. A value of `0` or less would print `On Time` instead.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>conditional-statements</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O18" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P18" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>1</v>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>Overdue</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>On Time</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Overdue</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>On Time</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>Overdue</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>Overdue</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE18" t="inlineStr">
         <is>
           <t>Overdue</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AG18" t="inlineStr">
         <is>
           <t>days_late = int(input())
-if days_late &gt; 0:
+if days_late &gt; 0:    # any positive number of days counts as overdue
     print("Overdue")
 else:
     print("On Time")</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Python - Temperature Comfort Check</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>A smart thermostat decides whether a room feels hot based on the current temperature. Write a program that reads a temperature in Celsius and prints whether it is hot or comfortable, using 30 as the threshold for hot.
-### Input Format
-- Line 1: Temperature in Celsius
-### Output Format
-```
-Hot
-```
 ### Example Walkthrough
 In the sample, the temperature is `35`. Since `35 &gt; 30`, the program prints `Hot`. A temperature of `30` or below would print `Comfortable` instead.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>conditional-statements</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O19" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P19" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="b">
+        <v>1</v>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Comfortable</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Comfortable</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>30.01</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>29.99</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>Comfortable</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>Comfortable</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE19" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AG19" t="inlineStr">
         <is>
           <t>temp = float(input())
-if temp &gt; 30:
+if temp &gt; 30:     # above 30 degrees is treated as hot
     print("Hot")
 else:
     print("Comfortable")</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Python - Temperature Alert</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>A weather station's alert board flashes a warning whenever the recorded temperature crosses into dangerously hot territory, defined as anything above 35 degrees.
 Write a program that reads the current temperature as a decimal number and prints `Hot` if it is strictly greater than 35, and `Normal` otherwise.
-### Input Format
-- Line 1: Temperature
-### Output Format
-```
-Hot
-```
 ### Example Walkthrough
 In the sample, the temperature is 36. Since 36 is greater than 35, the program prints `Hot`. A temperature of exactly 35 would instead print `Normal`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>conditional-statements</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O20" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P20" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="b">
+        <v>1</v>
+      </c>
+      <c r="R20" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD20" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE20" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AG20" t="inlineStr">
         <is>
           <t>t=float(input())
-print("Hot" if t&gt;35 else "Normal")</t>
+print("Hot" if t&gt;35 else "Normal")   # ternary check against the heat threshold</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Python - Largest of Two</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>A scoreboard app compares two contestants' scores after every round and highlights whichever one is ahead, breaking ties in favor of the first contestant.
 Write a program that reads two scores and prints the larger of the two; if they are equal, print the first score.
-### Input Format
-- Line 1: First score
-- Line 2: Second score
-### Output Format
-```
-5
-```
 ### Example Walkthrough
 In the sample, the first score is 5 and the second is 3. Since 5 is greater than or equal to 3, the program prints `5`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>conditional-statements</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O21" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P21" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="b">
+        <v>1</v>
+      </c>
+      <c r="R21" t="inlineStr">
         <is>
           <t>5
 3</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>2
 9</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>7
 7</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>-1
 -5</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>0
 10</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>100
 99</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>-3
 4</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE21" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AG21" t="inlineStr">
         <is>
           <t>a=int(input())
 b=int(input())
-print(a if a&gt;=b else b)</t>
+print(a if a&gt;=b else b)   # ternary picks whichever value is bigger</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Python - Parking Fee Tier</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>A mall's parking lot charges by vehicle type with a free grace period. Write a program that reads the number of hours a vehicle was parked and the vehicle type ('car' or 'bike'), then prints the total parking fee. Bikes get the first 2 hours free and are charged Rs. 5 per hour after that. Cars get only the first 1 hour free and are charged Rs. 10 per hour after that.
-### Input Format
-- Line 1: Hours parked
-- Line 2: Vehicle type ('car' or 'bike')
-### Output Format
-```
-0
-```
 ### Example Walkthrough
 In the sample, a bike is parked for `1` hour, well within its `2`-hour free window, so the fee is `0` and the program prints `0`. Parking for `5` hours would instead charge `(5 - 2) x 5 = 15`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>nested-conditions</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O22" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P22" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>1</v>
+      </c>
+      <c r="R22" t="inlineStr">
         <is>
           <t>1
 car</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>5
 car</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>2
 bike</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>6
 bike</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>0
 car</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>1
 bike</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>10
 car</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE22" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG22" t="inlineStr">
         <is>
           <t>hours = int(input())
 vehicle_type = input()
 if vehicle_type == "bike":
-    free_hours = 2
+    free_hours = 2      # bikes get more free hours
     rate = 5
 else:
     free_hours = 1
     rate = 10
 if hours &gt; free_hours:
-    fee = (hours - free_hours) * rate
+    fee = (hours - free_hours) * rate   # charge only for hours beyond the free limit
 else:
     fee = 0
 print(fee)</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Python - BMI Category</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>A fitness app classifies a member's BMI into a category, but seniors get slightly lower thresholds. Write a program that reads a BMI value and the member's age, then prints the BMI category. For members aged 60 or above, the boundaries are lowered by 1: 'Underweight' below 17, 'Normal' from 17 up to 24, 'Overweight' from 24 up to 28, and 'Obese' from 28 upward. For members under 60, the usual boundaries apply: 'Underweight' below 18.5, 'Normal' from 18.5 up to 25, 'Overweight' from 25 up to 30, and 'Obese' from 30 upward.
-### Input Format
-- Line 1: BMI value
-- Line 2: Age
-### Output Format
-```
-Normal
-```
 ### Example Walkthrough
 In the sample, the BMI is `22` and the age is `30`, so the under-60 boundaries apply. Since `22` falls between `18.5` and `25`, the category is `Normal`, and the program prints `Normal`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>nested-conditions</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O23" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P23" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="b">
+        <v>1</v>
+      </c>
+      <c r="R23" t="inlineStr">
         <is>
           <t>22
 30</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>18
 65</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>17.5
 70</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>16.5
 65</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>Underweight</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>26
 62</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>Overweight</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>29
 61</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>Obese</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD23" t="inlineStr">
         <is>
           <t>32
 40</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE23" t="inlineStr">
         <is>
           <t>Obese</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG23" t="inlineStr">
         <is>
           <t>bmi = float(input())
 age = int(input())
-if age &gt;= 60:
+if age &gt;= 60:                 # senior citizens use stricter BMI cutoffs
     if bmi &lt; 17:
         category = 'Underweight'
     elif bmi &lt; 24:
@@ -4567,7 +4051,7 @@
         category = 'Overweight'
     else:
         category = 'Obese'
-else:
+else:                          # standard adult BMI cutoffs
     if bmi &lt; 18.5:
         category = 'Underweight'
     elif bmi &lt; 25:
@@ -4580,844 +4064,809 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Python - Ticket Pricing by Age Group</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>An amusement park prices tickets by age group and adds a weekend surcharge. Write a program that reads a visitor's age and whether the visit is on a weekend ('yes' or 'no'), then prints the final ticket price. The base price by age is: free (0) under 5, 100 from 5 up to 18, 200 from 18 up to 60, and 150 from 60 upward. If the visit is on a weekend, a flat surcharge of 50 is added to any non-zero base price; a free ticket stays free.
-### Input Format
-- Line 1: Age
-- Line 2: Is weekend ('yes' or 'no')
-### Output Format
-```
-0
-```
 ### Example Walkthrough
 In the sample, the age is `3` and it is not a weekend. Since the age is under `5`, the base price is `0`, and a free ticket stays free even with a surcharge, so the program prints `0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>nested-conditions</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O24" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P24" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="b">
+        <v>1</v>
+      </c>
+      <c r="R24" t="inlineStr">
         <is>
           <t>3
 yes</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>10
 no</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>10
 yes</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>30
 no</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>30
 yes</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>65
 yes</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD24" t="inlineStr">
         <is>
           <t>4
 no</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AG24" t="inlineStr">
         <is>
           <t>age = int(input())
 is_weekend = input()
 if age &lt; 5:
-    price = 0
+    price = 0            # children under 5 enter free
 elif age &lt; 18:
     price = 100
 elif age &lt; 60:
     price = 200
 else:
-    price = 150
+    price = 150           # senior pricing
 if is_weekend == "yes" and price &gt; 0:
-    price += 50
+    price += 50           # weekend surcharge, skipped for free tickets
 print(price)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Python - Exam Result with Attendance</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>A college only passes a student if their marks clear 40 and their attendance is at least 75 percent. Write a program that reads a student's marks and attendance percentage, then prints whether the student passed.
-### Input Format
-- Line 1: Marks
-- Line 2: Attendance percentage
-### Output Format
-```
-Pass
-```
 ### Example Walkthrough
 In the sample, the marks are `65` and the attendance is `80`. Since `65 &gt;= 40` and `80 &gt;= 75` are both `True`, the program prints `Pass`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>truthiness-and-boolean-logic</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O25" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P25" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="b">
+        <v>1</v>
+      </c>
+      <c r="R25" t="inlineStr">
         <is>
           <t>60
 80</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>60
 50</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>30
 90</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>39.9
 90</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>40
 74.9</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>40
 75</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD25" t="inlineStr">
         <is>
           <t>100
 100</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE25" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AG25" t="inlineStr">
         <is>
           <t>marks = float(input())
 attendance = float(input())
-if marks &gt;= 40 and attendance &gt;= 75:
+if marks &gt;= 40 and attendance &gt;= 75:   # both conditions must hold to pass
     print("Pass")
 else:
     print("Fail")</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Python - Seat Belt Reminder</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>A car's dashboard shows a seat belt warning only while the car is moving and the belt is unfastened. Write a program that reads the car's speed and whether the seat belt is fastened (1 for yes, 0 for no), then prints whether the warning should be shown.
-### Input Format
-- Line 1: Speed
-- Line 2: Seat belt fastened (1 or 0)
-### Output Format
-```
-Show Warning
-```
 ### Example Walkthrough
 In the sample, the speed is `40` and the belt flag is `0`. Since the car is moving and the belt is unfastened, the program prints `Show Warning`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>truthiness-and-boolean-logic</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O26" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P26" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="b">
+        <v>1</v>
+      </c>
+      <c r="R26" t="inlineStr">
         <is>
           <t>40
 0</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>Show Warning</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>No Warning</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>40
 1</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>No Warning</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>0.1
 0</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>Show Warning</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>10
 1</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>No Warning</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>0
 1</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>No Warning</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>100
 0</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE26" t="inlineStr">
         <is>
           <t>Show Warning</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AG26" t="inlineStr">
         <is>
           <t>speed = float(input())
 belt_fastened = int(input())
-if speed &gt; 0 and belt_fastened == 0:
+if speed &gt; 0 and belt_fastened == 0:   # moving without the seat belt fastened
     print("Show Warning")
 else:
     print("No Warning")</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Python - Login Attempts Lockout</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>A banking app locks accounts after too many failed login attempts, but admin accounts are given a much higher threshold. Write a program that reads the number of failed login attempts and whether the account is an admin account ('yes' or 'no'), then prints the account status. Regular accounts are locked once attempts exceed 3; admin accounts are locked only once attempts exceed 10. Print 'Locked' if the account is locked, otherwise print 'Allowed'.
-### Input Format
-- Line 1: Failed login attempts
-- Line 2: Is admin account ('yes' or 'no')
-### Output Format
-```
-Allowed
-```
 ### Example Walkthrough
 In the sample, there are `2` failed attempts on a non-admin account. Since `2` does not exceed the regular threshold of `3`, the program prints `Allowed`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>nested-conditions</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O27" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P27" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="b">
+        <v>1</v>
+      </c>
+      <c r="R27" t="inlineStr">
         <is>
           <t>2
 no</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>Allowed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>4
 no</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>3
 no</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>Allowed</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>10
 yes</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>Allowed</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>11
 yes</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>5
 yes</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>Allowed</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>0
 no</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE27" t="inlineStr">
         <is>
           <t>Allowed</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AG27" t="inlineStr">
         <is>
           <t>attempts = int(input())
 is_admin = input()
 if is_admin == "yes":
-    status = "Locked" if attempts &gt; 10 else "Allowed"
+    status = "Locked" if attempts &gt; 10 else "Allowed"   # admins get a higher attempt limit
 else:
-    status = "Locked" if attempts &gt; 3 else "Allowed"
+    status = "Locked" if attempts &gt; 3 else "Allowed"    # stricter limit for regular users
 print(status)</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Python - Shipping Cost Bracket</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>A delivery company charges shipping cost by weight bracket, with a discount for premium members. Write a program that reads a package's weight in kilograms and the customer's membership status ('Premium' or 'Regular'), then prints the shipping cost. The regular bracket price is 50 for up to 1 kg, 100 for up to 5 kg, and 200 for anything heavier. Premium members get a flat 30 percent discount off the regular bracket price, rounded down to the nearest whole number.
-### Input Format
-- Line 1: Weight in kilograms
-- Line 2: Membership status ('Premium' or 'Regular')
-### Output Format
-```
-50
-```
 ### Example Walkthrough
 In the sample, the weight is `0.5` kg for a Regular member. Since `0.5` is at most `1` kg, the regular bracket price of `50` applies with no discount, so the program prints `50`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>nested-conditions</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O28" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P28" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="b">
+        <v>1</v>
+      </c>
+      <c r="R28" t="inlineStr">
         <is>
           <t>0.5
 Regular</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>0.5
 Premium</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>3
 Regular</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>3
 Premium</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>7
 Regular</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>7
 Premium</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>140</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>1
 Premium</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE28" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AG28" t="inlineStr">
         <is>
           <t>weight = float(input())
 membership_status = input()
@@ -5428,1360 +4877,1127 @@
 else:
     price = 200
 if membership_status == "Premium":
-    price = int(price * 0.7)
+    price = int(price * 0.7)   # premium members get a 30% discount
 print(price)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Python - Grade Band</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>A results portal converts every numeric score into a letter grade band before displaying it on the student dashboard. The bands are: 90 or above is `A`, 75 up to 89 is `B`, 50 up to 74 is `C`, and anything below 50 is `Needs Practice`.
 Write a program that reads a student's score and prints the correct grade band using these cutoffs.
-### Input Format
-- Line 1: Score
-### Output Format
-```
-A
-```
 ### Example Walkthrough
 In the sample, the score is 95. Since 95 is 90 or above, the program prints `A`. A score of 80 would print `B`, 65 would print `C`, and 40 would print `Needs Practice`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>nested-conditions</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O29" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>1</v>
+      </c>
+      <c r="R29" t="inlineStr">
         <is>
           <t>95</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>Needs Practice</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AG29" t="inlineStr">
         <is>
           <t>s=int(input())
 if s&gt;=90: print("A")
 elif s&gt;=75: print("B")
 elif s&gt;=50: print("C")
-else: print("Needs Practice")</t>
+else: print("Needs Practice")   # falls through here whenever score &lt; 50</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Python - Login Role</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>A campus portal decides what a logged-in user can see based on two things: their account status and their role. If the account is not `active`, the user gets no access regardless of role. If it is active, an `admin` gets full access, a `student` gets learning access, and anyone else gets limited access.
 Write a program that reads the role and the status, then prints exactly one of `Full Access`, `Learning Access`, `Limited Access`, or `No Access` following this rule.
-### Input Format
-- Line 1: Role
-- Line 2: Status (`active` or any other value)
-### Output Format
-```
-Full Access
-```
 ### Example Walkthrough
 In the sample, the role is admin and the status is active. Since the status is active and the role is admin, the program prints `Full Access`.
 ### Constraints
 - Role and status are valid strings with no leading or trailing spaces.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>nested-conditions</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O30" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P30" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="b">
+        <v>1</v>
+      </c>
+      <c r="R30" t="inlineStr">
         <is>
           <t>admin
 active</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>Full Access</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>admin
 inactive</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>No Access</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>student
 active</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>Learning Access</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>student
 inactive</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>No Access</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>guest
 active</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>Limited Access</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>mentor
 active</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>Limited Access</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD30" t="inlineStr">
         <is>
           <t>guest
 inactive</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE30" t="inlineStr">
         <is>
           <t>No Access</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AG30" t="inlineStr">
         <is>
           <t>role=input()
 status=input()
 if status=="active":
-    if role=="admin": print("Full Access")
+    if role=="admin": print("Full Access")        # admin role gets full access
     elif role=="student": print("Learning Access")
-    else: print("Limited Access")
-else: print("No Access")</t>
+    else: print("Limited Access")                  # any other role while active
+else: print("No Access")   # inactive accounts have no access regardless of role</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Python - Day Code Type</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>A hostel mess planning tool reads a three-letter day code and needs to know whether it falls on a weekday or a weekend, so it can plan the right menu. `SAT` and `SUN` are weekends, `MON` through `FRI` are weekdays, and anything else is not a recognized code.
 Write a program that reads a three-letter day code and prints `Weekend`, `Weekday`, or `Unknown` accordingly. The check is case-sensitive.
-### Input Format
-- Line 1: Day code
-### Output Format
-```
-Weekday
-```
 ### Example Walkthrough
 In the sample, the code is MON. Since MON is one of the weekday codes, the program prints `Weekday`. A code of SAT would print `Weekend`, and a lowercase code like sat would print `Unknown` since the check is case-sensitive.
 ### Constraints
 - Day code is a valid string with no leading or trailing spaces.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>match-case</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O31" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="b">
+        <v>1</v>
+      </c>
+      <c r="R31" t="inlineStr">
         <is>
           <t>MON</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>Weekday</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>Weekend</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>SUN</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>Weekend</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>FRI</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>Weekday</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>XYZ</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>TUE</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>Weekday</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE31" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AG31" t="inlineStr">
         <is>
           <t>code=input()
-if code in ("SAT","SUN"): print("Weekend")
+if code in ("SAT","SUN"): print("Weekend")                       # membership test against a tuple
 elif code in ("MON","TUE","WED","THU","FRI"): print("Weekday")
 else: print("Unknown")</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Python - Loan Eligibility Check</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>A bank approves a personal loan only after checking the applicant's age first, and only checks their income if the age requirement is met. Write a program that reads an applicant's age and monthly income, then prints the loan decision: 'Rejected: Age' if the applicant is under 21, 'Rejected: Income' if they are old enough but earn less than 20000, and 'Approved' otherwise.
-### Input Format
-- Line 1: Age
-- Line 2: Monthly income
-### Output Format
-```
-Approved
-```
 ### Example Walkthrough
 In the sample, the age is `25` and the income is `30000`. Since the age clears `21` and the income clears `20000`, the program prints `Approved`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>nested-conditions</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O32" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P32" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="b">
+        <v>1</v>
+      </c>
+      <c r="R32" t="inlineStr">
         <is>
           <t>25
 30000</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>19
 50000</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>Rejected: Age</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>30
 15000</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>Rejected: Income</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>21
 20000</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>20
 99999</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>Rejected: Age</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>21
 19999</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>Rejected: Income</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>50
 100000</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE32" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG32" t="inlineStr">
         <is>
           <t>age = int(input())
 income = float(input())
 if age &lt; 21:
-    print("Rejected: Age")
+    print("Rejected: Age")       # underage applicants are rejected first
 else:
     if income &lt; 20000:
-        print("Rejected: Income")
+        print("Rejected: Income")   # nested check runs only when age passed
     else:
         print("Approved")</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Python - Guarded Withdrawal Validation</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>An ATM's validation logic checks the most obvious failure cases first, before checking anything else, so that clearer error messages are shown earlier. Write a program that reads an account balance and a withdrawal amount, then prints 'Invalid Amount' if the amount is zero or negative, 'Insufficient Funds' if the amount is positive but exceeds the balance, and 'Approved' otherwise.
-### Input Format
-- Line 1: Account balance
-- Line 2: Withdrawal amount
-### Output Format
-```
-Approved
-```
 ### Example Walkthrough
 In the sample, the balance is `5000` and the requested amount is `2000`. The amount is positive and does not exceed the balance, so the program prints `Approved`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>conditional-statements</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O33" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P33" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="b">
+        <v>1</v>
+      </c>
+      <c r="R33" t="inlineStr">
         <is>
           <t>5000
 1000</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>5000
 -200</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>Invalid Amount</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>500
 800</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>Insufficient Funds</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>500
 0</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>Invalid Amount</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>500
 500</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>500
 501</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC33" t="inlineStr">
         <is>
           <t>Insufficient Funds</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD33" t="inlineStr">
         <is>
           <t>500
 -5</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE33" t="inlineStr">
         <is>
           <t>Invalid Amount</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG33" t="inlineStr">
         <is>
           <t>balance = float(input())
 amount = float(input())
-if amount &lt;= 0:
+if amount &lt;= 0:            # guard clause: reject non-positive amounts first
     print("Invalid Amount")
-elif amount &gt; balance:
+elif amount &gt; balance:     # guard clause: reject if funds are insufficient
     print("Insufficient Funds")
 else:
     print("Approved")</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Python - Nested Membership Discount Eligibility</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>A store's loyalty programme gives different discounts depending on both the customer's membership tier and their purchase amount. Write a program that reads a membership tier as the text 'Gold' or 'Silver' and a purchase amount, then prints the discount percentage: a Gold member gets 20 percent if the purchase is at least 2000, otherwise 10 percent; a Silver member gets 10 percent if the purchase is at least 2000, otherwise 5 percent.
-### Input Format
-- Line 1: Membership tier ('Gold' or 'Silver')
-- Line 2: Purchase amount
-### Output Format
-```
-Discount: 20%
-```
 ### Example Walkthrough
 In the sample, the tier is `Gold` and the purchase is `2500`. Since the tier is Gold and the amount is at least `2000`, the discount is `20` percent, so the program prints `Discount: 20%`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>nested-conditions</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O34" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P34" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="b">
+        <v>1</v>
+      </c>
+      <c r="R34" t="inlineStr">
         <is>
           <t>Gold
 2500</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>Discount: 20%</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>Gold
 1000</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>Discount: 10%</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>Silver
 3000</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>Discount: 10%</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>Gold
 1999</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>Discount: 10%</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>Silver
 1999</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>Discount: 5%</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>Silver
 2000</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>Discount: 10%</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD34" t="inlineStr">
         <is>
           <t>Gold
 0</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE34" t="inlineStr">
         <is>
           <t>Discount: 10%</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AG34" t="inlineStr">
         <is>
           <t>tier = input()
 amount = float(input())
 if tier == 'Gold':
     if amount &gt;= 2000:
-        discount = 20
+        discount = 20        # gold tier, large purchase
     else:
-        discount = 10
+        discount = 10        # gold tier, smaller purchase
 else:
     if amount &gt;= 2000:
-        discount = 10
+        discount = 10        # non-gold tier, large purchase
     else:
-        discount = 5
+        discount = 5         # non-gold tier, smaller purchase
 print(f"Discount: {discount}%")</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Python - Grade with Attendance Override</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>A college's grading policy first computes the marks-based grade, but caps any grade at 'C' if the student's attendance was below 75 percent, regardless of how high their marks were. Write a program that reads a student's marks and attendance percentage, then prints the final grade following this policy, using the usual marks bands: 'A' for 90 or above, 'B' for 75 up to 90, 'C' for 60 up to 75, and 'F' below 60.
-### Input Format
-- Line 1: Marks
-- Line 2: Attendance percentage
-### Output Format
-```
-B
-```
 ### Example Walkthrough
 In the sample, the marks are `80` and the attendance is `85`. The marks-based grade is `B` (`75` up to `90`), and since attendance is at least `75`, no override applies, so the program prints `B`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>nested-conditions</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O35" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P35" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="b">
+        <v>1</v>
+      </c>
+      <c r="R35" t="inlineStr">
         <is>
           <t>95
 80</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>95
 50</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>45
 50</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>74.9
 90</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>90
 74.9</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>30
 50</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC35" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD35" t="inlineStr">
         <is>
           <t>75
 75</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE35" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AG35" t="inlineStr">
         <is>
           <t>marks = float(input())
 attendance = float(input())
@@ -6793,1020 +6009,978 @@
     grade = 'C'
 else:
     grade = 'F'
-if attendance &lt; 75 and grade != 'F':
+if attendance &lt; 75 and grade != 'F':   # low attendance downgrades a passing grade
     grade = 'C'
 print(grade)</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Python - Tiered Speeding Fine Calculator</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Traffic police calculate a fine based on how far over the speed limit a vehicle was travelling. Write a program that reads a vehicle's speed and the road's speed limit, then prints the fine: 0 if the vehicle was at or under the limit, 500 if it exceeded the limit by up to 20, and 1500 if it exceeded the limit by more than 20.
-### Input Format
-- Line 1: Vehicle speed
-- Line 2: Speed limit
-### Output Format
-```
-Fine: 1500
-```
 ### Example Walkthrough
 In the sample, the speed is `90` against a limit of `60`, so the vehicle is `30` over. Since `30` is more than `20` over the limit, the fine is `1500`, and the program prints `Fine: 1500`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>conditional-statements</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O36" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P36" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="b">
+        <v>1</v>
+      </c>
+      <c r="R36" t="inlineStr">
         <is>
           <t>60
 60</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>Fine: 0</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>75
 60</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>Fine: 500</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>100
 60</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>Fine: 1500</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>59
 60</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>Fine: 0</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>80
 60</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>Fine: 500</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>81
 60</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC36" t="inlineStr">
         <is>
           <t>Fine: 1500</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD36" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE36" t="inlineStr">
         <is>
           <t>Fine: 0</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AG36" t="inlineStr">
         <is>
           <t>speed = float(input())
 limit = float(input())
-over = speed - limit
+over = speed - limit   # how much the speed exceeds the limit
 if over &lt;= 0:
     fine = 0
 elif over &lt;= 20:
     fine = 500
 else:
-    fine = 1500
+    fine = 1500          # steepest fine for large violations
 print("Fine:", fine)</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Python - Parity and Sign Combined</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>A number-classifier tool labels a number by both its sign and its parity in one combined word. Write a program that reads an integer and prints one of 'Positive Even', 'Positive Odd', 'Negative Even', 'Negative Odd', or 'Zero', using ternary (conditional) expressions rather than full if-else blocks.
-### Input Format
-- Line 1: Integer
-### Output Format
-```
-Positive Even
-```
 ### Example Walkthrough
 In the sample, the number is `8`. It is greater than `0`, so the sign is `Positive`, and since `8 % 2 == 0`, it is `Even`, so the program prints `Positive Even`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>conditional-expressions</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O37" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P37" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="b">
+        <v>1</v>
+      </c>
+      <c r="R37" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>Positive Even</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>Negative Odd</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>Zero</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>Negative Even</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>Positive Odd</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC37" t="inlineStr">
         <is>
           <t>Positive Even</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD37" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE37" t="inlineStr">
         <is>
           <t>Negative Odd</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AG37" t="inlineStr">
         <is>
           <t>n = int(input())
-sign = "Zero" if n == 0 else ("Positive" if n &gt; 0 else "Negative")
-label = sign if n == 0 else sign + " " + ("Even" if n % 2 == 0 else "Odd")
+sign = "Zero" if n == 0 else ("Positive" if n &gt; 0 else "Negative")   # nested ternary decides the sign
+label = sign if n == 0 else sign + " " + ("Even" if n % 2 == 0 else "Odd")   # skip the parity label for zero
 print(label)</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Python - Insurance Claim Approval</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>An insurance company auto-approves small claims with valid policies, refers large claims for manual review, and rejects anything from an inactive policy outright. Write a program that reads whether the policy is active (1 for yes, 0 for no) and the claim amount, then prints the decision: 'Rejected: Inactive Policy' if the policy is inactive; otherwise, for an active policy, 'Auto Approved' if the claim is at most 10000, and 'Manual Review' if it is more than 10000.
-### Input Format
-- Line 1: Policy active (1 or 0)
-- Line 2: Claim amount
-### Output Format
-```
-Auto Approved
-```
 ### Example Walkthrough
 In the sample, the policy is active (`1`) and the claim is `5000`. Since the policy is active and the claim is at most `10000`, the program prints `Auto Approved`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>nested-conditions</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O38" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P38" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q38" t="b">
+        <v>1</v>
+      </c>
+      <c r="R38" t="inlineStr">
         <is>
           <t>1
 5000</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>Auto Approved</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>0
 5000</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>Rejected: Inactive Policy</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>1
 25000</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>Manual Review</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>0
 1</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>Rejected: Inactive Policy</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>1
 10000</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA38" t="inlineStr">
         <is>
           <t>Auto Approved</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB38" t="inlineStr">
         <is>
           <t>1
 10001</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC38" t="inlineStr">
         <is>
           <t>Manual Review</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD38" t="inlineStr">
         <is>
           <t>0
 999999</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE38" t="inlineStr">
         <is>
           <t>Rejected: Inactive Policy</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AG38" t="inlineStr">
         <is>
           <t>is_active = int(input())
 claim_amount = float(input())
 if is_active == 0:
-    print("Rejected: Inactive Policy")
+    print("Rejected: Inactive Policy")   # guard clause: inactive policies rejected first
 else:
     if claim_amount &lt;= 10000:
         print("Auto Approved")
     else:
-        print("Manual Review")</t>
+        print("Manual Review")           # large claims need manual review</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Python - Scholarship Check</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>A scholarship committee reviews each applicant's marks percentage and attendance percentage together. An applicant is fully `Eligible` only when both marks are at least 85 and attendance is at least 90; if only one of the two conditions is met they go on a `Waitlist`; if neither is met they are `Not Eligible`.
 Write a program that reads the marks percentage and the attendance percentage, then prints `Eligible`, `Waitlist`, or `Not Eligible` following this rule.
-### Input Format
-- Line 1: Marks percentage
-- Line 2: Attendance percentage
-### Output Format
-```
-Eligible
-```
 ### Example Walkthrough
 In the sample, marks are 90 and attendance is 95. Since marks are at least 85 and attendance is at least 90, both conditions are met, so the program prints `Eligible`. Marks of 85 with attendance of 89 would meet only one condition and print `Waitlist`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>nested-conditions</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O39" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P39" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="b">
+        <v>1</v>
+      </c>
+      <c r="R39" t="inlineStr">
         <is>
           <t>90
 95</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>Eligible</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>85
 89</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>Waitlist</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>80
 95</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>Waitlist</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>70
 80</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>Not Eligible</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>99
 90</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>Eligible</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>85
 90</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC39" t="inlineStr">
         <is>
           <t>Eligible</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD39" t="inlineStr">
         <is>
           <t>84
 89</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE39" t="inlineStr">
         <is>
           <t>Not Eligible</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AG39" t="inlineStr">
         <is>
           <t>m=int(input())
 a=int(input())
-if m&gt;=85 and a&gt;=90: print("Eligible")
-elif m&gt;=85 or a&gt;=90: print("Waitlist")
+if m&gt;=85 and a&gt;=90: print("Eligible")        # both marks and attendance must be high
+elif m&gt;=85 or a&gt;=90: print("Waitlist")       # only one of the two conditions met
 else: print("Not Eligible")</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Python - Triangle Type</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>A geometry teaching app checks three side lengths entered by a student and classifies the shape before drawing it. The sides must each be positive and satisfy the triangle inequality (no side can be greater than or equal to the sum of the other two), otherwise the shape is `Invalid`. A valid triangle with all three sides equal is `Equilateral`, one with exactly two equal sides is `Isosceles`, and one with all different sides is `Scalene`.
 Write a program that reads three side lengths and prints `Invalid`, `Equilateral`, `Isosceles`, or `Scalene` following this rule.
-### Input Format
-- Line 1: Side a
-- Line 2: Side b
-- Line 3: Side c
-### Output Format
-```
-Equilateral
-```
 ### Example Walkthrough
 In the sample, the sides are 3, 3, and 3. They form a valid triangle and all three sides are equal, so the program prints `Equilateral`. Sides 3, 3, 4 would print `Isosceles`, and sides 1, 2, 3 would print `Invalid` since 1 + 2 is not greater than 3.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>conditional-statements</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O40" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P40" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="b">
+        <v>1</v>
+      </c>
+      <c r="R40" t="inlineStr">
         <is>
           <t>3
 3
 3</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>Equilateral</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>3
 3
 4</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>Isosceles</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>3
 4
 5</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>Scalene</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>1
 2
 3</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>Invalid</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>5
 1
 1</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>Invalid</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>0
 1
 1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC40" t="inlineStr">
         <is>
           <t>Invalid</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD40" t="inlineStr">
         <is>
           <t>10
 6
 6</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE40" t="inlineStr">
         <is>
           <t>Isosceles</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AG40" t="inlineStr">
         <is>
           <t>a=int(input()); b=int(input()); c=int(input())
-if a+b&lt;=c or a+c&lt;=b or b+c&lt;=a or a&lt;=0 or b&lt;=0 or c&lt;=0: print("Invalid")
+if a+b&lt;=c or a+c&lt;=b or b+c&lt;=a or a&lt;=0 or b&lt;=0 or c&lt;=0: print("Invalid")   # triangle inequality and positivity check
 elif a==b==c: print("Equilateral")
 elif a==b or b==c or a==c: print("Isosceles")
 else: print("Scalene")</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Python - Safe Division Decision</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>A calculator widget divides two numbers a user enters, but must guard against a zero denominator instead of letting the app crash.
 Write a program that reads two decimal numbers and prints their quotient (first divided by second); if the second number is 0, print `Cannot divide` instead.
-### Input Format
-- Line 1: First number
-- Line 2: Second number
-### Output Format
-```
-5.0
-```
 ### Example Walkthrough
 In the sample, the numbers are 10 and 2. Since 2 is not 0, the program divides 10 by 2 and prints `5.0`. If the second number were 0, it would print `Cannot divide` instead.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>control-flow</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>input-validation</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O41" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P41" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="b">
+        <v>1</v>
+      </c>
+      <c r="R41" t="inlineStr">
         <is>
           <t>10
 2</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>5
 0</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>Cannot divide</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>0
 5</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>7
 2</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>-6
 3</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>-2.0</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>6
 -3</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC41" t="inlineStr">
         <is>
           <t>-2.0</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD41" t="inlineStr">
         <is>
           <t>1
 4</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE41" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AG41" t="inlineStr">
         <is>
           <t>a=float(input())
 b=float(input())
-print("Cannot divide" if b==0 else a/b)</t>
+print("Cannot divide" if b==0 else a/b)   # guard against division by zero</t>
         </is>
       </c>
     </row>
